--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -441,8 +441,11 @@
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -523,79 +526,105 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Crude Set E PW FV</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Crude Set E EV %</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Crude Set E position</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>robustness</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>DHT</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" s="2" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D2" t="n">
-        <v>13.34</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-18.7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-14.2</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>15.02</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>12.39</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-24.4</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>WEIGHT-ROBUST</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all four weight sets</t>
+      <c r="D2" s="2" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>-17.1</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>-32.3</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-24.8</v>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>HOLD under Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>
@@ -606,16 +635,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48.1</v>
+        <v>49.94</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
       </c>
       <c r="D3" t="n">
-        <v>32.53</v>
+        <v>40.02</v>
       </c>
       <c r="E3" t="n">
-        <v>-32.4</v>
+        <v>-19.9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -623,10 +652,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>34.97</v>
+        <v>30.46</v>
       </c>
       <c r="H3" t="n">
-        <v>-27.3</v>
+        <v>-39</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -634,10 +663,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>38.03</v>
+        <v>33.35</v>
       </c>
       <c r="K3" t="n">
-        <v>-20.9</v>
+        <v>-33.2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -645,24 +674,35 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>29.47</v>
+        <v>25.28</v>
       </c>
       <c r="N3" t="n">
-        <v>-38.7</v>
+        <v>-49.4</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-41.4</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all four weight sets</t>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 5 weight sets</t>
         </is>
       </c>
     </row>
@@ -673,16 +713,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
       </c>
       <c r="D4" t="n">
-        <v>23.87</v>
+        <v>28.82</v>
       </c>
       <c r="E4" t="n">
-        <v>-30.8</v>
+        <v>-16.9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -690,10 +730,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>25.75</v>
+        <v>21.71</v>
       </c>
       <c r="H4" t="n">
-        <v>-25.4</v>
+        <v>-37.4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -701,10 +741,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>28.1</v>
+        <v>23.86</v>
       </c>
       <c r="K4" t="n">
-        <v>-18.6</v>
+        <v>-31.2</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -712,24 +752,35 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>21.52</v>
+        <v>17.84</v>
       </c>
       <c r="N4" t="n">
-        <v>-37.6</v>
+        <v>-48.6</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-40.1</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all four weight sets</t>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 5 weight sets</t>
         </is>
       </c>
     </row>
@@ -740,16 +791,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76.8</v>
+        <v>77.78</v>
       </c>
       <c r="C5" t="n">
         <v>79.5</v>
       </c>
       <c r="D5" t="n">
-        <v>52.08</v>
+        <v>60.19</v>
       </c>
       <c r="E5" t="n">
-        <v>-32.2</v>
+        <v>-22.6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -757,10 +808,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>54.59</v>
+        <v>52.84</v>
       </c>
       <c r="H5" t="n">
-        <v>-28.9</v>
+        <v>-32.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -768,10 +819,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>57.66</v>
+        <v>55.06</v>
       </c>
       <c r="K5" t="n">
-        <v>-24.9</v>
+        <v>-29.2</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -779,24 +830,35 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>49.01</v>
+        <v>48.91</v>
       </c>
       <c r="N5" t="n">
-        <v>-36.2</v>
+        <v>-37.1</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-33.2</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all four weight sets</t>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 5 weight sets</t>
         </is>
       </c>
     </row>
@@ -807,63 +869,74 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>70.5</v>
+        <v>64.33</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>75</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>69.31</v>
+        <v>79.59</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-1.7</v>
+        <v>23.7</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>71.44</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>67.12</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>73.44</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>66.97</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>WEIGHT-DRIVEN</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD under Set A/Set B/Set C; TRIM/SHORT under Set D</t>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>BUY under Set A/Set B/Set C/Set E; HOLD under Set D</t>
         </is>
       </c>
     </row>
@@ -874,16 +947,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.4</v>
+        <v>5.56</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>2.28</v>
+        <v>3.33</v>
       </c>
       <c r="E7" t="n">
-        <v>-57.8</v>
+        <v>-40.1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -891,10 +964,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2.49</v>
+        <v>2.61</v>
       </c>
       <c r="H7" t="n">
-        <v>-53.8</v>
+        <v>-53</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -902,10 +975,10 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="K7" t="n">
-        <v>-49</v>
+        <v>-49.1</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -913,24 +986,347 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="N7" t="n">
-        <v>-62.6</v>
+        <v>-59.9</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-54.6</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all four weight sets</t>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 5 weight sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TEN</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="C8" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="H8" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>58.64</v>
+      </c>
+      <c r="K8" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>55.16</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>56</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>position BUY across all 5 weight sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CMBT</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>BUY under Set A; HOLD under Set B/Set C/Set D/Set E</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BRUT</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>-43.1</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>BUY under Set A/Set B/Set C; TRIM/SHORT under Set D; HOLD under Set E</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CAPT</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>BUY under Set A/Set C; HOLD under Set B; TRIM/SHORT under Set D/Set E</t>
         </is>
       </c>
     </row>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -551,80 +551,80 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>DHT</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>16.53</v>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="B2" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="C2" t="n">
         <v>16</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>15.77</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>-22.5</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>-17.1</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>-32.3</v>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>-24.8</v>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>WEIGHT-DRIVEN</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>HOLD under Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
+      <c r="D2" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-22.4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-33.3</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-29.7</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-38</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-33.9</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 5 weight sets</t>
         </is>
       </c>
     </row>
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49.94</v>
+        <v>53.11</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
       </c>
       <c r="D3" t="n">
-        <v>40.02</v>
+        <v>32.09</v>
       </c>
       <c r="E3" t="n">
-        <v>-19.9</v>
+        <v>-39.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>30.46</v>
+        <v>26.06</v>
       </c>
       <c r="H3" t="n">
-        <v>-39</v>
+        <v>-50.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>33.35</v>
+        <v>28.07</v>
       </c>
       <c r="K3" t="n">
-        <v>-33.2</v>
+        <v>-47.2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>25.28</v>
+        <v>23.52</v>
       </c>
       <c r="N3" t="n">
-        <v>-49.4</v>
+        <v>-55.7</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>29.25</v>
+        <v>25.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>-41.4</v>
+        <v>-51.6</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -713,16 +713,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34.7</v>
+        <v>36.75</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
       </c>
       <c r="D4" t="n">
-        <v>28.82</v>
+        <v>22.91</v>
       </c>
       <c r="E4" t="n">
-        <v>-16.9</v>
+        <v>-37.7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>21.71</v>
+        <v>18.43</v>
       </c>
       <c r="H4" t="n">
-        <v>-37.4</v>
+        <v>-49.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>23.86</v>
+        <v>19.92</v>
       </c>
       <c r="K4" t="n">
-        <v>-31.2</v>
+        <v>-45.8</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>17.84</v>
+        <v>16.53</v>
       </c>
       <c r="N4" t="n">
-        <v>-48.6</v>
+        <v>-55</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>20.8</v>
+        <v>18.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>-40.1</v>
+        <v>-50.6</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.78</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C5" t="n">
         <v>79.5</v>
       </c>
       <c r="D5" t="n">
-        <v>60.19</v>
+        <v>52.93</v>
       </c>
       <c r="E5" t="n">
-        <v>-22.6</v>
+        <v>-35.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>52.84</v>
+        <v>48.23</v>
       </c>
       <c r="H5" t="n">
-        <v>-32.1</v>
+        <v>-41.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>55.06</v>
+        <v>49.79</v>
       </c>
       <c r="K5" t="n">
-        <v>-29.2</v>
+        <v>-39.6</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>48.91</v>
+        <v>46.29</v>
       </c>
       <c r="N5" t="n">
-        <v>-37.1</v>
+        <v>-43.8</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>51.94</v>
+        <v>48</v>
       </c>
       <c r="Q5" t="n">
-        <v>-33.2</v>
+        <v>-41.8</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -869,16 +869,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>64.33</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>75</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>79.59</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>23.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -886,32 +886,32 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>71.44</v>
+        <v>67.88</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>11</v>
+        <v>0.4</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>73.92</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>14.9</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>67.12</v>
+        <v>65.69</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4.3</v>
+        <v>-2.8</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -919,14 +919,14 @@
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>70.45999999999999</v>
+        <v>67.61</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>BUY under Set A/Set B/Set C/Set E; HOLD under Set D</t>
+          <t>BUY under Set A; HOLD under Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>
@@ -947,16 +947,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.56</v>
+        <v>5.81</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>3.33</v>
+        <v>2.72</v>
       </c>
       <c r="E7" t="n">
-        <v>-40.1</v>
+        <v>-53.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2.61</v>
+        <v>2.27</v>
       </c>
       <c r="H7" t="n">
-        <v>-53</v>
+        <v>-60.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2.83</v>
+        <v>2.42</v>
       </c>
       <c r="K7" t="n">
-        <v>-49.1</v>
+        <v>-58.4</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="N7" t="n">
-        <v>-59.9</v>
+        <v>-64</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>-54.6</v>
+        <v>-61.2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1025,16 +1025,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35.37</v>
+        <v>37.37</v>
       </c>
       <c r="C8" t="n">
         <v>51.5</v>
       </c>
       <c r="D8" t="n">
-        <v>64.34999999999999</v>
+        <v>56.36</v>
       </c>
       <c r="E8" t="n">
-        <v>81.90000000000001</v>
+        <v>50.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>56.14</v>
+        <v>51.15</v>
       </c>
       <c r="H8" t="n">
-        <v>58.7</v>
+        <v>36.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>58.64</v>
+        <v>52.9</v>
       </c>
       <c r="K8" t="n">
-        <v>65.8</v>
+        <v>41.6</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>51.8</v>
+        <v>49.05</v>
       </c>
       <c r="N8" t="n">
-        <v>46.4</v>
+        <v>31.3</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>55.16</v>
+        <v>50.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>56</v>
+        <v>36.3</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1103,64 +1103,64 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>14.05</v>
+        <v>14.56</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>16.59</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>15.56</v>
+        <v>14.15</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>10.7</v>
+        <v>-2.8</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>14.34</v>
+        <v>13.38</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>2</v>
+        <v>-8.1</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>14.71</v>
+        <v>13.64</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>4.7</v>
+        <v>-6.3</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>13.67</v>
+        <v>13.06</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-2.7</v>
+        <v>-10.3</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>14.18</v>
+        <v>13.34</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.9</v>
+        <v>-8.4</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>BUY under Set A; HOLD under Set B/Set C/Set D/Set E</t>
+          <t>HOLD under Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>
@@ -1181,16 +1181,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.17</v>
+        <v>5.29</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>7.13</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10.24</v>
+        <v>6.2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>98.09999999999999</v>
+        <v>17.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1198,32 +1198,32 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>5.54</v>
+        <v>3.3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>7.2</v>
+        <v>-37.7</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>6.95</v>
+        <v>4.26</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>34.5</v>
+        <v>-19.4</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2.94</v>
+        <v>2.04</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-43.1</v>
+        <v>-61.4</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1231,14 +1231,14 @@
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>4.91</v>
+        <v>3.12</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-5</v>
+        <v>-41</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>BUY under Set A/Set B/Set C; TRIM/SHORT under Set D; HOLD under Set E</t>
+          <t>BUY under Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>12.49</v>
+        <v>13.28</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>17.16</v>
+        <v>13.14</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>37.4</v>
+        <v>-1.1</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>12.46</v>
+        <v>10.23</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-0.3</v>
+        <v>-23</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>13.87</v>
+        <v>11.19</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>11</v>
+        <v>-15.7</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>9.890000000000001</v>
+        <v>9</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-20.8</v>
+        <v>-32.2</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>11.85</v>
+        <v>10.07</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-5.1</v>
+        <v>-24.2</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>BUY under Set A/Set C; HOLD under Set B; TRIM/SHORT under Set D/Set E</t>
+          <t>HOLD under Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.18</v>
+        <v>17.2</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -577,7 +577,7 @@
         <v>11.46</v>
       </c>
       <c r="H2" t="n">
-        <v>-33.3</v>
+        <v>-33.4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         <v>11.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>-33.9</v>
+        <v>-34</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53.11</v>
+        <v>53.1</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
@@ -666,7 +666,7 @@
         <v>28.07</v>
       </c>
       <c r="K3" t="n">
-        <v>-47.2</v>
+        <v>-47.1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>25.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>-51.6</v>
+        <v>-51.5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.75</v>
+        <v>36.8</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
@@ -733,7 +733,7 @@
         <v>18.43</v>
       </c>
       <c r="H4" t="n">
-        <v>-49.8</v>
+        <v>-49.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>19.92</v>
       </c>
       <c r="K4" t="n">
-        <v>-45.8</v>
+        <v>-45.9</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>16.53</v>
       </c>
       <c r="N4" t="n">
-        <v>-55</v>
+        <v>-55.1</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.81</v>
+        <v>5.8</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -967,7 +967,7 @@
         <v>2.27</v>
       </c>
       <c r="H7" t="n">
-        <v>-60.9</v>
+        <v>-60.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>2.42</v>
       </c>
       <c r="K7" t="n">
-        <v>-58.4</v>
+        <v>-58.3</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>2.09</v>
       </c>
       <c r="N7" t="n">
-        <v>-64</v>
+        <v>-63.9</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37.37</v>
+        <v>37.14</v>
       </c>
       <c r="C8" t="n">
         <v>51.5</v>
@@ -1034,7 +1034,7 @@
         <v>56.36</v>
       </c>
       <c r="E8" t="n">
-        <v>50.8</v>
+        <v>51.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>51.15</v>
       </c>
       <c r="H8" t="n">
-        <v>36.9</v>
+        <v>37.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>52.9</v>
       </c>
       <c r="K8" t="n">
-        <v>41.6</v>
+        <v>42.4</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>49.05</v>
       </c>
       <c r="N8" t="n">
-        <v>31.3</v>
+        <v>32.1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>50.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>36.3</v>
+        <v>37.1</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>14.56</v>
+        <v>14.6</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>16.59</v>
@@ -1112,7 +1112,7 @@
         <v>14.15</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-2.8</v>
+        <v>-3.1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>13.38</v>
+        <v>13.39</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>-8.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>13.64</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-6.3</v>
+        <v>-6.6</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>13.06</v>
+        <v>13.07</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-10.3</v>
+        <v>-10.5</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>13.34</v>
+        <v>13.35</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-8.4</v>
+        <v>-8.6</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.29</v>
+        <v>5.3</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>7.13</v>
@@ -1190,7 +1190,7 @@
         <v>6.2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>3.3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>-37.7</v>
+        <v>-37.8</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>4.26</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-19.4</v>
+        <v>-19.6</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>3.12</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-41</v>
+        <v>-41.2</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>13.28</v>
+        <v>13.31</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>
@@ -1268,7 +1268,7 @@
         <v>13.14</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>10.23</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-23</v>
+        <v>-23.2</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>11.19</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-15.7</v>
+        <v>-15.9</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-32.2</v>
+        <v>-32.4</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>10.07</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-24.2</v>
+        <v>-24.4</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.2</v>
+        <v>16.93</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -566,7 +566,7 @@
         <v>13.34</v>
       </c>
       <c r="E2" t="n">
-        <v>-22.4</v>
+        <v>-21.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         <v>11.46</v>
       </c>
       <c r="H2" t="n">
-        <v>-33.4</v>
+        <v>-32.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         <v>12.08</v>
       </c>
       <c r="K2" t="n">
-        <v>-29.7</v>
+        <v>-28.6</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         <v>10.66</v>
       </c>
       <c r="N2" t="n">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         <v>11.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>-34</v>
+        <v>-33</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53.1</v>
+        <v>52.23</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
@@ -644,7 +644,7 @@
         <v>32.09</v>
       </c>
       <c r="E3" t="n">
-        <v>-39.6</v>
+        <v>-38.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         <v>26.06</v>
       </c>
       <c r="H3" t="n">
-        <v>-50.9</v>
+        <v>-50.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>28.07</v>
       </c>
       <c r="K3" t="n">
-        <v>-47.1</v>
+        <v>-46.3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>23.52</v>
       </c>
       <c r="N3" t="n">
-        <v>-55.7</v>
+        <v>-55</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>25.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>-51.5</v>
+        <v>-50.7</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.8</v>
+        <v>36.56</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
@@ -722,7 +722,7 @@
         <v>22.91</v>
       </c>
       <c r="E4" t="n">
-        <v>-37.7</v>
+        <v>-37.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>18.43</v>
       </c>
       <c r="H4" t="n">
-        <v>-49.9</v>
+        <v>-49.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>19.92</v>
       </c>
       <c r="K4" t="n">
-        <v>-45.9</v>
+        <v>-45.5</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>16.53</v>
       </c>
       <c r="N4" t="n">
-        <v>-55.1</v>
+        <v>-54.8</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>18.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>-50.6</v>
+        <v>-50.3</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>82.40000000000001</v>
+        <v>82.98</v>
       </c>
       <c r="C5" t="n">
         <v>79.5</v>
@@ -800,7 +800,7 @@
         <v>52.93</v>
       </c>
       <c r="E5" t="n">
-        <v>-35.8</v>
+        <v>-36.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>48.23</v>
       </c>
       <c r="H5" t="n">
-        <v>-41.5</v>
+        <v>-41.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>49.79</v>
       </c>
       <c r="K5" t="n">
-        <v>-39.6</v>
+        <v>-40</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>46.29</v>
       </c>
       <c r="N5" t="n">
-        <v>-43.8</v>
+        <v>-44.2</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>48</v>
       </c>
       <c r="Q5" t="n">
-        <v>-41.8</v>
+        <v>-42.2</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>69.27</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>75</v>
@@ -878,7 +878,7 @@
         <v>73.18000000000001</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>67.88</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.4</v>
+        <v>-2</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>69.65000000000001</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -911,18 +911,18 @@
         <v>65.69</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-2.8</v>
+        <v>-5.2</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
         <v>67.61</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>BUY under Set A; HOLD under Set B/Set C/Set D/Set E</t>
+          <t>BUY under Set A; HOLD under Set B/Set C/Set E; TRIM/SHORT under Set D</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -956,7 +956,7 @@
         <v>2.72</v>
       </c>
       <c r="E7" t="n">
-        <v>-53.2</v>
+        <v>-54</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>2.27</v>
       </c>
       <c r="H7" t="n">
-        <v>-60.8</v>
+        <v>-61.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>2.42</v>
       </c>
       <c r="K7" t="n">
-        <v>-58.3</v>
+        <v>-59</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>2.09</v>
       </c>
       <c r="N7" t="n">
-        <v>-63.9</v>
+        <v>-64.5</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>-61.2</v>
+        <v>-61.8</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37.14</v>
+        <v>38.22</v>
       </c>
       <c r="C8" t="n">
         <v>51.5</v>
@@ -1034,7 +1034,7 @@
         <v>56.36</v>
       </c>
       <c r="E8" t="n">
-        <v>51.7</v>
+        <v>47.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>51.15</v>
       </c>
       <c r="H8" t="n">
-        <v>37.7</v>
+        <v>33.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>52.9</v>
       </c>
       <c r="K8" t="n">
-        <v>42.4</v>
+        <v>38.4</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>49.05</v>
       </c>
       <c r="N8" t="n">
-        <v>32.1</v>
+        <v>28.3</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>50.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>37.1</v>
+        <v>33.2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1097,80 +1097,80 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>CMBT</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="C9" s="2" t="n">
+      <c r="B9" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="C9" t="n">
         <v>16.59</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" t="n">
         <v>14.15</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
+      <c r="E9" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>13.39</v>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
+      <c r="H9" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>13.64</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
+      <c r="K9" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
         <v>13.07</v>
       </c>
-      <c r="N9" s="2" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="n">
+      <c r="N9" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
         <v>13.35</v>
       </c>
-      <c r="Q9" s="2" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>WEIGHT-DRIVEN</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>HOLD under Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
+      <c r="Q9" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 5 weight sets</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.3</v>
+        <v>5.66</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>7.13</v>
@@ -1190,7 +1190,7 @@
         <v>6.2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>17.1</v>
+        <v>9.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>3.3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>-37.8</v>
+        <v>-41.7</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>4.26</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-19.6</v>
+        <v>-24.7</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>2.04</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-61.4</v>
+        <v>-63.9</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>3.12</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-41.2</v>
+        <v>-44.9</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>13.31</v>
+        <v>13.06</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>
@@ -1268,7 +1268,7 @@
         <v>13.14</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-1.3</v>
+        <v>0.6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>10.23</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-23.2</v>
+        <v>-21.7</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>11.19</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-15.9</v>
+        <v>-14.3</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-32.4</v>
+        <v>-31.1</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>10.07</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-24.4</v>
+        <v>-22.9</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.93</v>
+        <v>17.76</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -566,7 +566,7 @@
         <v>13.34</v>
       </c>
       <c r="E2" t="n">
-        <v>-21.2</v>
+        <v>-24.9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         <v>11.46</v>
       </c>
       <c r="H2" t="n">
-        <v>-32.3</v>
+        <v>-35.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         <v>12.08</v>
       </c>
       <c r="K2" t="n">
-        <v>-28.6</v>
+        <v>-32</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         <v>10.66</v>
       </c>
       <c r="N2" t="n">
-        <v>-37</v>
+        <v>-40</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         <v>11.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>-33</v>
+        <v>-36.1</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52.23</v>
+        <v>54.94</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
@@ -644,7 +644,7 @@
         <v>32.09</v>
       </c>
       <c r="E3" t="n">
-        <v>-38.6</v>
+        <v>-41.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         <v>26.06</v>
       </c>
       <c r="H3" t="n">
-        <v>-50.1</v>
+        <v>-52.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>28.07</v>
       </c>
       <c r="K3" t="n">
-        <v>-46.3</v>
+        <v>-48.9</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>23.52</v>
       </c>
       <c r="N3" t="n">
-        <v>-55</v>
+        <v>-57.2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>25.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>-50.7</v>
+        <v>-53.2</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.56</v>
+        <v>38.13</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
@@ -722,7 +722,7 @@
         <v>22.91</v>
       </c>
       <c r="E4" t="n">
-        <v>-37.3</v>
+        <v>-39.9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>18.43</v>
       </c>
       <c r="H4" t="n">
-        <v>-49.6</v>
+        <v>-51.7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>19.92</v>
       </c>
       <c r="K4" t="n">
-        <v>-45.5</v>
+        <v>-47.8</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>16.53</v>
       </c>
       <c r="N4" t="n">
-        <v>-54.8</v>
+        <v>-56.7</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>18.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>-50.3</v>
+        <v>-52.3</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>82.98</v>
+        <v>88.48</v>
       </c>
       <c r="C5" t="n">
         <v>79.5</v>
@@ -800,7 +800,7 @@
         <v>52.93</v>
       </c>
       <c r="E5" t="n">
-        <v>-36.2</v>
+        <v>-40.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>48.23</v>
       </c>
       <c r="H5" t="n">
-        <v>-41.9</v>
+        <v>-45.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>49.79</v>
       </c>
       <c r="K5" t="n">
-        <v>-40</v>
+        <v>-43.7</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>46.29</v>
       </c>
       <c r="N5" t="n">
-        <v>-44.2</v>
+        <v>-47.7</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>48</v>
       </c>
       <c r="Q5" t="n">
-        <v>-42.2</v>
+        <v>-45.8</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>69.27</v>
+        <v>72.45</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>75</v>
@@ -878,29 +878,29 @@
         <v>73.18000000000001</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
         <v>67.88</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>-2</v>
+        <v>-6.3</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>69.65000000000001</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.5</v>
+        <v>-3.9</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>65.69</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-5.2</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -922,11 +922,11 @@
         <v>67.61</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-2.4</v>
+        <v>-6.7</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>BUY under Set A; HOLD under Set B/Set C/Set E; TRIM/SHORT under Set D</t>
+          <t>HOLD under Set A/Set C; TRIM/SHORT under Set B/Set D/Set E</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.9</v>
+        <v>6.17</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -956,7 +956,7 @@
         <v>2.72</v>
       </c>
       <c r="E7" t="n">
-        <v>-54</v>
+        <v>-56</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>2.27</v>
       </c>
       <c r="H7" t="n">
-        <v>-61.5</v>
+        <v>-63.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>2.42</v>
       </c>
       <c r="K7" t="n">
-        <v>-59</v>
+        <v>-60.8</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>2.09</v>
       </c>
       <c r="N7" t="n">
-        <v>-64.5</v>
+        <v>-66.09999999999999</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>-61.8</v>
+        <v>-63.5</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38.22</v>
+        <v>39.66</v>
       </c>
       <c r="C8" t="n">
         <v>51.5</v>
@@ -1034,7 +1034,7 @@
         <v>56.36</v>
       </c>
       <c r="E8" t="n">
-        <v>47.5</v>
+        <v>42.1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>51.15</v>
       </c>
       <c r="H8" t="n">
-        <v>33.8</v>
+        <v>29</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>52.9</v>
       </c>
       <c r="K8" t="n">
-        <v>38.4</v>
+        <v>33.4</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>49.05</v>
       </c>
       <c r="N8" t="n">
-        <v>28.3</v>
+        <v>23.7</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>50.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.2</v>
+        <v>28.4</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14.93</v>
+        <v>15.57</v>
       </c>
       <c r="C9" t="n">
         <v>16.59</v>
@@ -1112,7 +1112,7 @@
         <v>14.15</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.2</v>
+        <v>-9.1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>13.39</v>
       </c>
       <c r="H9" t="n">
-        <v>-10.3</v>
+        <v>-14</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>13.64</v>
       </c>
       <c r="K9" t="n">
-        <v>-8.6</v>
+        <v>-12.4</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>13.07</v>
       </c>
       <c r="N9" t="n">
-        <v>-12.5</v>
+        <v>-16.1</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>13.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>-10.6</v>
+        <v>-14.3</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.66</v>
+        <v>5.58</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>7.13</v>
@@ -1190,7 +1190,7 @@
         <v>6.2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9.6</v>
+        <v>11.2</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>3.3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>-41.7</v>
+        <v>-40.9</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>4.26</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-24.7</v>
+        <v>-23.6</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>2.04</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-63.9</v>
+        <v>-63.4</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>3.12</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-44.9</v>
+        <v>-44.1</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>13.06</v>
+        <v>13</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>
@@ -1268,7 +1268,7 @@
         <v>13.14</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>10.23</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-21.7</v>
+        <v>-21.3</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>11.19</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-14.3</v>
+        <v>-13.9</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-31.1</v>
+        <v>-30.8</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>10.07</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-22.9</v>
+        <v>-22.6</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.76</v>
+        <v>17.31</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -566,7 +566,7 @@
         <v>13.34</v>
       </c>
       <c r="E2" t="n">
-        <v>-24.9</v>
+        <v>-22.9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         <v>11.46</v>
       </c>
       <c r="H2" t="n">
-        <v>-35.5</v>
+        <v>-33.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         <v>12.08</v>
       </c>
       <c r="K2" t="n">
-        <v>-32</v>
+        <v>-30.2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         <v>10.66</v>
       </c>
       <c r="N2" t="n">
-        <v>-40</v>
+        <v>-38.4</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         <v>11.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>-36.1</v>
+        <v>-34.4</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54.94</v>
+        <v>54.2</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
@@ -644,7 +644,7 @@
         <v>32.09</v>
       </c>
       <c r="E3" t="n">
-        <v>-41.6</v>
+        <v>-40.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         <v>26.06</v>
       </c>
       <c r="H3" t="n">
-        <v>-52.6</v>
+        <v>-51.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>28.07</v>
       </c>
       <c r="K3" t="n">
-        <v>-48.9</v>
+        <v>-48.2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>23.52</v>
       </c>
       <c r="N3" t="n">
-        <v>-57.2</v>
+        <v>-56.6</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>25.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>-53.2</v>
+        <v>-52.5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.13</v>
+        <v>36.92</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
@@ -722,7 +722,7 @@
         <v>22.91</v>
       </c>
       <c r="E4" t="n">
-        <v>-39.9</v>
+        <v>-37.9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>18.43</v>
       </c>
       <c r="H4" t="n">
-        <v>-51.7</v>
+        <v>-50.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>19.92</v>
       </c>
       <c r="K4" t="n">
-        <v>-47.8</v>
+        <v>-46</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>16.53</v>
       </c>
       <c r="N4" t="n">
-        <v>-56.7</v>
+        <v>-55.2</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>18.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>-52.3</v>
+        <v>-50.8</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>88.48</v>
+        <v>86.17</v>
       </c>
       <c r="C5" t="n">
         <v>79.5</v>
@@ -800,7 +800,7 @@
         <v>52.93</v>
       </c>
       <c r="E5" t="n">
-        <v>-40.2</v>
+        <v>-38.6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>48.23</v>
       </c>
       <c r="H5" t="n">
-        <v>-45.5</v>
+        <v>-44</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>49.79</v>
       </c>
       <c r="K5" t="n">
-        <v>-43.7</v>
+        <v>-42.2</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>46.29</v>
       </c>
       <c r="N5" t="n">
-        <v>-47.7</v>
+        <v>-46.3</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>48</v>
       </c>
       <c r="Q5" t="n">
-        <v>-45.8</v>
+        <v>-44.3</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>72.45</v>
+        <v>70.72</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>75</v>
@@ -878,7 +878,7 @@
         <v>73.18000000000001</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -889,18 +889,18 @@
         <v>67.88</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>-6.3</v>
+        <v>-4</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>69.65000000000001</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-3.9</v>
+        <v>-1.5</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>65.69</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-9.300000000000001</v>
+        <v>-7.1</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -922,11 +922,11 @@
         <v>67.61</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-6.7</v>
+        <v>-4.4</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A/Set C; TRIM/SHORT under Set B/Set D/Set E</t>
+          <t>HOLD under Set A/Set B/Set C/Set E; TRIM/SHORT under Set D</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.17</v>
+        <v>6.09</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -956,7 +956,7 @@
         <v>2.72</v>
       </c>
       <c r="E7" t="n">
-        <v>-56</v>
+        <v>-55.4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>2.27</v>
       </c>
       <c r="H7" t="n">
-        <v>-63.1</v>
+        <v>-62.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>2.42</v>
       </c>
       <c r="K7" t="n">
-        <v>-60.8</v>
+        <v>-60.3</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>2.09</v>
       </c>
       <c r="N7" t="n">
-        <v>-66.09999999999999</v>
+        <v>-65.59999999999999</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>-63.5</v>
+        <v>-63</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39.66</v>
+        <v>38.83</v>
       </c>
       <c r="C8" t="n">
         <v>51.5</v>
@@ -1034,7 +1034,7 @@
         <v>56.36</v>
       </c>
       <c r="E8" t="n">
-        <v>42.1</v>
+        <v>45.1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>51.15</v>
       </c>
       <c r="H8" t="n">
-        <v>29</v>
+        <v>31.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>52.9</v>
       </c>
       <c r="K8" t="n">
-        <v>33.4</v>
+        <v>36.2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>49.05</v>
       </c>
       <c r="N8" t="n">
-        <v>23.7</v>
+        <v>26.3</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>50.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.4</v>
+        <v>31.1</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1103,16 +1103,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.57</v>
+        <v>15.44</v>
       </c>
       <c r="C9" t="n">
         <v>16.59</v>
       </c>
       <c r="D9" t="n">
-        <v>14.15</v>
+        <v>13.87</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.1</v>
+        <v>-10.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>13.39</v>
+        <v>13.1</v>
       </c>
       <c r="H9" t="n">
-        <v>-14</v>
+        <v>-15.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13.64</v>
+        <v>13.36</v>
       </c>
       <c r="K9" t="n">
-        <v>-12.4</v>
+        <v>-13.5</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13.07</v>
+        <v>12.78</v>
       </c>
       <c r="N9" t="n">
-        <v>-16.1</v>
+        <v>-17.2</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>13.35</v>
+        <v>13.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>-14.3</v>
+        <v>-15.4</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.58</v>
+        <v>5.54</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>7.13</v>
@@ -1190,7 +1190,7 @@
         <v>6.2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11.2</v>
+        <v>12</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>3.3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>-40.9</v>
+        <v>-40.5</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>4.26</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-23.6</v>
+        <v>-23.1</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>2.04</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-63.4</v>
+        <v>-63.1</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>3.12</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-44.1</v>
+        <v>-43.7</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>
@@ -1268,7 +1268,7 @@
         <v>13.14</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1.1</v>
+        <v>-1.1</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>10.23</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-21.3</v>
+        <v>-23</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>11.19</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-13.9</v>
+        <v>-15.7</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-30.8</v>
+        <v>-32.2</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>10.07</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-22.6</v>
+        <v>-24.2</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -427,7 +427,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.31</v>
+        <v>18.18</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -566,7 +566,7 @@
         <v>13.34</v>
       </c>
       <c r="E2" t="n">
-        <v>-22.9</v>
+        <v>-26.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         <v>11.46</v>
       </c>
       <c r="H2" t="n">
-        <v>-33.8</v>
+        <v>-37</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         <v>12.08</v>
       </c>
       <c r="K2" t="n">
-        <v>-30.2</v>
+        <v>-33.5</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         <v>10.66</v>
       </c>
       <c r="N2" t="n">
-        <v>-38.4</v>
+        <v>-41.4</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         <v>11.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>-34.4</v>
+        <v>-37.6</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54.2</v>
+        <v>56.73</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
@@ -644,7 +644,7 @@
         <v>32.09</v>
       </c>
       <c r="E3" t="n">
-        <v>-40.8</v>
+        <v>-43.4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         <v>26.06</v>
       </c>
       <c r="H3" t="n">
-        <v>-51.9</v>
+        <v>-54.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>28.07</v>
       </c>
       <c r="K3" t="n">
-        <v>-48.2</v>
+        <v>-50.5</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>23.52</v>
       </c>
       <c r="N3" t="n">
-        <v>-56.6</v>
+        <v>-58.5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>25.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>-52.5</v>
+        <v>-54.6</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.92</v>
+        <v>38.38</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
@@ -722,7 +722,7 @@
         <v>22.91</v>
       </c>
       <c r="E4" t="n">
-        <v>-37.9</v>
+        <v>-40.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>18.43</v>
       </c>
       <c r="H4" t="n">
-        <v>-50.1</v>
+        <v>-52</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>19.92</v>
       </c>
       <c r="K4" t="n">
-        <v>-46</v>
+        <v>-48.1</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>16.53</v>
       </c>
       <c r="N4" t="n">
-        <v>-55.2</v>
+        <v>-56.9</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>18.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>-50.8</v>
+        <v>-52.7</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86.17</v>
+        <v>88.12</v>
       </c>
       <c r="C5" t="n">
         <v>79.5</v>
       </c>
       <c r="D5" t="n">
-        <v>52.93</v>
+        <v>54.21</v>
       </c>
       <c r="E5" t="n">
-        <v>-38.6</v>
+        <v>-38.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>48.23</v>
+        <v>49.52</v>
       </c>
       <c r="H5" t="n">
-        <v>-44</v>
+        <v>-43.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>49.79</v>
+        <v>51.07</v>
       </c>
       <c r="K5" t="n">
-        <v>-42.2</v>
+        <v>-42</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>46.29</v>
+        <v>47.58</v>
       </c>
       <c r="N5" t="n">
-        <v>-46.3</v>
+        <v>-46</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>48</v>
+        <v>49.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>-44.3</v>
+        <v>-44.1</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>70.72</v>
+        <v>72.27</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>75</v>
@@ -878,7 +878,7 @@
         <v>73.18000000000001</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -889,18 +889,18 @@
         <v>67.88</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>-4</v>
+        <v>-6.1</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>69.65000000000001</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-1.5</v>
+        <v>-3.6</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>65.69</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-7.1</v>
+        <v>-9.1</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -922,11 +922,11 @@
         <v>67.61</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-4.4</v>
+        <v>-6.4</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A/Set B/Set C/Set E; TRIM/SHORT under Set D</t>
+          <t>HOLD under Set A/Set C; TRIM/SHORT under Set B/Set D/Set E</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.09</v>
+        <v>6.29</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -956,7 +956,7 @@
         <v>2.72</v>
       </c>
       <c r="E7" t="n">
-        <v>-55.4</v>
+        <v>-56.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>2.27</v>
       </c>
       <c r="H7" t="n">
-        <v>-62.7</v>
+        <v>-63.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>2.42</v>
       </c>
       <c r="K7" t="n">
-        <v>-60.3</v>
+        <v>-61.5</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>2.09</v>
       </c>
       <c r="N7" t="n">
-        <v>-65.59999999999999</v>
+        <v>-66.7</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>-63</v>
+        <v>-64.2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1025,16 +1025,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38.83</v>
+        <v>39.75</v>
       </c>
       <c r="C8" t="n">
         <v>51.5</v>
       </c>
       <c r="D8" t="n">
-        <v>56.36</v>
+        <v>57.6</v>
       </c>
       <c r="E8" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>51.15</v>
+        <v>52.39</v>
       </c>
       <c r="H8" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>52.9</v>
+        <v>54.14</v>
       </c>
       <c r="K8" t="n">
         <v>36.2</v>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>49.05</v>
+        <v>50.3</v>
       </c>
       <c r="N8" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>50.92</v>
+        <v>52.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.44</v>
+        <v>15.78</v>
       </c>
       <c r="C9" t="n">
         <v>16.59</v>
@@ -1112,7 +1112,7 @@
         <v>13.87</v>
       </c>
       <c r="E9" t="n">
-        <v>-10.2</v>
+        <v>-12.1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>13.1</v>
       </c>
       <c r="H9" t="n">
-        <v>-15.1</v>
+        <v>-17</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>13.36</v>
       </c>
       <c r="K9" t="n">
-        <v>-13.5</v>
+        <v>-15.4</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>12.78</v>
       </c>
       <c r="N9" t="n">
-        <v>-17.2</v>
+        <v>-19</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>13.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>-15.4</v>
+        <v>-17.2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.54</v>
+        <v>5.5727</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>7.13</v>
@@ -1190,7 +1190,7 @@
         <v>6.2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>3.3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>-40.5</v>
+        <v>-40.8</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>4.26</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-23.1</v>
+        <v>-23.5</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>2.04</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-63.1</v>
+        <v>-63.3</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>3.12</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-43.7</v>
+        <v>-44</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>13.28</v>
+        <v>13.3972</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>
@@ -1268,7 +1268,7 @@
         <v>13.14</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-1.1</v>
+        <v>-1.9</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>10.23</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-23</v>
+        <v>-23.7</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>11.19</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-15.7</v>
+        <v>-16.5</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-32.2</v>
+        <v>-32.8</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>10.07</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-24.2</v>
+        <v>-24.9</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -1031,10 +1031,10 @@
         <v>51.5</v>
       </c>
       <c r="D8" t="n">
-        <v>57.6</v>
+        <v>57.64</v>
       </c>
       <c r="E8" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>52.39</v>
+        <v>52.43</v>
       </c>
       <c r="H8" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>54.14</v>
+        <v>54.18</v>
       </c>
       <c r="K8" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>50.3</v>
+        <v>50.33</v>
       </c>
       <c r="N8" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>52.16</v>
+        <v>52.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -1031,10 +1031,10 @@
         <v>51.5</v>
       </c>
       <c r="D8" t="n">
-        <v>57.64</v>
+        <v>56.46</v>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>52.43</v>
+        <v>51.65</v>
       </c>
       <c r="H8" t="n">
-        <v>31.9</v>
+        <v>29.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>54.18</v>
+        <v>53.24</v>
       </c>
       <c r="K8" t="n">
-        <v>36.3</v>
+        <v>33.9</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>50.33</v>
+        <v>49.77</v>
       </c>
       <c r="N8" t="n">
-        <v>26.6</v>
+        <v>25.2</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>52.2</v>
+        <v>51.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>31.3</v>
+        <v>29.5</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -427,7 +427,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.18</v>
+        <v>17.41</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -566,7 +566,7 @@
         <v>13.34</v>
       </c>
       <c r="E2" t="n">
-        <v>-26.6</v>
+        <v>-23.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         <v>11.46</v>
       </c>
       <c r="H2" t="n">
-        <v>-37</v>
+        <v>-34.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         <v>12.08</v>
       </c>
       <c r="K2" t="n">
-        <v>-33.5</v>
+        <v>-30.6</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         <v>10.66</v>
       </c>
       <c r="N2" t="n">
-        <v>-41.4</v>
+        <v>-38.8</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         <v>11.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>-37.6</v>
+        <v>-34.8</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56.73</v>
+        <v>53.88</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
@@ -644,7 +644,7 @@
         <v>32.09</v>
       </c>
       <c r="E3" t="n">
-        <v>-43.4</v>
+        <v>-40.4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         <v>26.06</v>
       </c>
       <c r="H3" t="n">
-        <v>-54.1</v>
+        <v>-51.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>28.07</v>
       </c>
       <c r="K3" t="n">
-        <v>-50.5</v>
+        <v>-47.9</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>23.52</v>
       </c>
       <c r="N3" t="n">
-        <v>-58.5</v>
+        <v>-56.3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>25.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>-54.6</v>
+        <v>-52.2</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.38</v>
+        <v>36.49</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
@@ -722,7 +722,7 @@
         <v>22.91</v>
       </c>
       <c r="E4" t="n">
-        <v>-40.3</v>
+        <v>-37.2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>18.43</v>
       </c>
       <c r="H4" t="n">
-        <v>-52</v>
+        <v>-49.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>19.92</v>
       </c>
       <c r="K4" t="n">
-        <v>-48.1</v>
+        <v>-45.4</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>16.53</v>
       </c>
       <c r="N4" t="n">
-        <v>-56.9</v>
+        <v>-54.7</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>18.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>-52.7</v>
+        <v>-50.2</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>88.12</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="C5" t="n">
         <v>79.5</v>
@@ -800,7 +800,7 @@
         <v>54.21</v>
       </c>
       <c r="E5" t="n">
-        <v>-38.5</v>
+        <v>-37.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>49.52</v>
       </c>
       <c r="H5" t="n">
-        <v>-43.8</v>
+        <v>-42.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>51.07</v>
       </c>
       <c r="K5" t="n">
-        <v>-42</v>
+        <v>-41.1</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>47.58</v>
       </c>
       <c r="N5" t="n">
-        <v>-46</v>
+        <v>-45.2</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>49.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>-44.1</v>
+        <v>-43.2</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>72.27</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>75</v>
@@ -878,7 +878,7 @@
         <v>73.18000000000001</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -889,18 +889,18 @@
         <v>67.88</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>-6.1</v>
+        <v>-3.1</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>69.65000000000001</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-3.6</v>
+        <v>-0.6</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>65.69</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-9.1</v>
+        <v>-6.2</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -922,11 +922,11 @@
         <v>67.61</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-6.4</v>
+        <v>-3.5</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A/Set C; TRIM/SHORT under Set B/Set D/Set E</t>
+          <t>HOLD under Set A/Set B/Set C/Set E; TRIM/SHORT under Set D</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.29</v>
+        <v>6.05</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -956,7 +956,7 @@
         <v>2.72</v>
       </c>
       <c r="E7" t="n">
-        <v>-56.8</v>
+        <v>-55.1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>2.27</v>
       </c>
       <c r="H7" t="n">
-        <v>-63.8</v>
+        <v>-62.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>2.42</v>
       </c>
       <c r="K7" t="n">
-        <v>-61.5</v>
+        <v>-60</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>2.09</v>
       </c>
       <c r="N7" t="n">
-        <v>-66.7</v>
+        <v>-65.40000000000001</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>-64.2</v>
+        <v>-62.8</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39.75</v>
+        <v>37.62</v>
       </c>
       <c r="C8" t="n">
         <v>51.5</v>
@@ -1034,7 +1034,7 @@
         <v>56.46</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>50.1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>51.65</v>
       </c>
       <c r="H8" t="n">
-        <v>29.9</v>
+        <v>37.3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>53.24</v>
       </c>
       <c r="K8" t="n">
-        <v>33.9</v>
+        <v>41.5</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>49.77</v>
       </c>
       <c r="N8" t="n">
-        <v>25.2</v>
+        <v>32.3</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>51.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>29.5</v>
+        <v>36.8</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.78</v>
+        <v>14.96</v>
       </c>
       <c r="C9" t="n">
         <v>16.59</v>
@@ -1112,7 +1112,7 @@
         <v>13.87</v>
       </c>
       <c r="E9" t="n">
-        <v>-12.1</v>
+        <v>-7.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>13.1</v>
       </c>
       <c r="H9" t="n">
-        <v>-17</v>
+        <v>-12.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>13.36</v>
       </c>
       <c r="K9" t="n">
-        <v>-15.4</v>
+        <v>-10.7</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>12.78</v>
       </c>
       <c r="N9" t="n">
-        <v>-19</v>
+        <v>-14.6</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>13.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>-17.2</v>
+        <v>-12.7</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.5727</v>
+        <v>5.5025</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>7.13</v>
@@ -1190,7 +1190,7 @@
         <v>6.2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11.3</v>
+        <v>12.8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>3.3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>-40.8</v>
+        <v>-40.1</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>4.26</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-23.5</v>
+        <v>-22.5</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>2.04</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-63.3</v>
+        <v>-62.8</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>3.12</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-44</v>
+        <v>-43.3</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>13.3972</v>
+        <v>12.718</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>
@@ -1268,7 +1268,7 @@
         <v>13.14</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-1.9</v>
+        <v>3.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>10.23</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-23.7</v>
+        <v>-19.6</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>11.19</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-16.5</v>
+        <v>-12</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-32.8</v>
+        <v>-29.2</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>10.07</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-24.9</v>
+        <v>-20.8</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -563,10 +563,10 @@
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>13.34</v>
+        <v>13.1</v>
       </c>
       <c r="E2" t="n">
-        <v>-23.4</v>
+        <v>-24.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>11.46</v>
+        <v>11.24</v>
       </c>
       <c r="H2" t="n">
-        <v>-34.2</v>
+        <v>-35.4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12.08</v>
+        <v>11.86</v>
       </c>
       <c r="K2" t="n">
-        <v>-30.6</v>
+        <v>-31.9</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -596,10 +596,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>10.66</v>
+        <v>10.45</v>
       </c>
       <c r="N2" t="n">
-        <v>-38.8</v>
+        <v>-40</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -607,10 +607,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>11.35</v>
+        <v>11.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>-34.8</v>
+        <v>-36</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>45</v>
       </c>
       <c r="D3" t="n">
-        <v>32.09</v>
+        <v>32.1</v>
       </c>
       <c r="E3" t="n">
         <v>-40.4</v>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>26.06</v>
+        <v>26.08</v>
       </c>
       <c r="H3" t="n">
         <v>-51.6</v>
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>28.07</v>
+        <v>28.08</v>
       </c>
       <c r="K3" t="n">
         <v>-47.9</v>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>23.52</v>
+        <v>23.54</v>
       </c>
       <c r="N3" t="n">
         <v>-56.3</v>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>25.73</v>
+        <v>25.74</v>
       </c>
       <c r="Q3" t="n">
         <v>-52.2</v>
@@ -719,10 +719,10 @@
         <v>30.5</v>
       </c>
       <c r="D4" t="n">
-        <v>22.91</v>
+        <v>22.8</v>
       </c>
       <c r="E4" t="n">
-        <v>-37.2</v>
+        <v>-37.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>18.43</v>
+        <v>18.33</v>
       </c>
       <c r="H4" t="n">
-        <v>-49.5</v>
+        <v>-49.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19.92</v>
+        <v>19.82</v>
       </c>
       <c r="K4" t="n">
-        <v>-45.4</v>
+        <v>-45.7</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>16.53</v>
+        <v>16.43</v>
       </c>
       <c r="N4" t="n">
-        <v>-54.7</v>
+        <v>-55</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>18.17</v>
+        <v>18.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>-50.2</v>
+        <v>-50.5</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
         <v>79.5</v>
       </c>
       <c r="D5" t="n">
-        <v>54.21</v>
+        <v>54.12</v>
       </c>
       <c r="E5" t="n">
-        <v>-37.5</v>
+        <v>-37.6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>49.52</v>
+        <v>49.44</v>
       </c>
       <c r="H5" t="n">
-        <v>-42.9</v>
+        <v>-43</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>51.07</v>
+        <v>50.99</v>
       </c>
       <c r="K5" t="n">
-        <v>-41.1</v>
+        <v>-41.2</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>47.58</v>
+        <v>47.51</v>
       </c>
       <c r="N5" t="n">
         <v>-45.2</v>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>49.28</v>
+        <v>49.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>-43.2</v>
+        <v>-43.3</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
         <v>75</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>73.18000000000001</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>67.88</v>
+        <v>68.03</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>-3.1</v>
+        <v>-2.9</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>69.65000000000001</v>
+        <v>69.81</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>65.69</v>
+        <v>65.84</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-6.2</v>
+        <v>-6</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>67.61</v>
+        <v>67.77</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-3.5</v>
+        <v>-3.3</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -953,10 +953,10 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="E7" t="n">
-        <v>-55.1</v>
+        <v>-54.4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="H7" t="n">
-        <v>-62.4</v>
+        <v>-61.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="K7" t="n">
-        <v>-60</v>
+        <v>-59.4</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="N7" t="n">
-        <v>-65.40000000000001</v>
+        <v>-64.8</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>-62.8</v>
+        <v>-62.2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         <v>51.5</v>
       </c>
       <c r="D8" t="n">
-        <v>56.46</v>
+        <v>56.56</v>
       </c>
       <c r="E8" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>51.65</v>
+        <v>51.74</v>
       </c>
       <c r="H8" t="n">
-        <v>37.3</v>
+        <v>37.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>53.24</v>
+        <v>53.34</v>
       </c>
       <c r="K8" t="n">
-        <v>41.5</v>
+        <v>41.8</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>49.77</v>
+        <v>49.85</v>
       </c>
       <c r="N8" t="n">
-        <v>32.3</v>
+        <v>32.5</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>51.48</v>
+        <v>51.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>36.8</v>
+        <v>37.1</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1109,10 +1109,10 @@
         <v>16.59</v>
       </c>
       <c r="D9" t="n">
-        <v>13.87</v>
+        <v>14.09</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.3</v>
+        <v>-5.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>13.1</v>
+        <v>13.33</v>
       </c>
       <c r="H9" t="n">
-        <v>-12.4</v>
+        <v>-10.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13.36</v>
+        <v>13.58</v>
       </c>
       <c r="K9" t="n">
-        <v>-10.7</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>12.78</v>
+        <v>13</v>
       </c>
       <c r="N9" t="n">
-        <v>-14.6</v>
+        <v>-13.1</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>13.06</v>
+        <v>13.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>-12.7</v>
+        <v>-11.2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>7.13</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6.2</v>
+        <v>6.21</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>12.8</v>
@@ -1201,7 +1201,7 @@
         <v>3.3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>-40.1</v>
+        <v>-40</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>-62.8</v>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -427,7 +427,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.41</v>
+        <v>17.89</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -566,7 +566,7 @@
         <v>13.1</v>
       </c>
       <c r="E2" t="n">
-        <v>-24.8</v>
+        <v>-26.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         <v>11.24</v>
       </c>
       <c r="H2" t="n">
-        <v>-35.4</v>
+        <v>-37.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         <v>11.86</v>
       </c>
       <c r="K2" t="n">
-        <v>-31.9</v>
+        <v>-33.7</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         <v>10.45</v>
       </c>
       <c r="N2" t="n">
-        <v>-40</v>
+        <v>-41.6</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         <v>11.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>-36</v>
+        <v>-37.8</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53.88</v>
+        <v>54.24</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
@@ -644,7 +644,7 @@
         <v>32.1</v>
       </c>
       <c r="E3" t="n">
-        <v>-40.4</v>
+        <v>-40.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         <v>26.08</v>
       </c>
       <c r="H3" t="n">
-        <v>-51.6</v>
+        <v>-51.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>28.08</v>
       </c>
       <c r="K3" t="n">
-        <v>-47.9</v>
+        <v>-48.2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>23.54</v>
       </c>
       <c r="N3" t="n">
-        <v>-56.3</v>
+        <v>-56.6</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>25.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>-52.2</v>
+        <v>-52.5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.49</v>
+        <v>36.93</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
@@ -722,7 +722,7 @@
         <v>22.8</v>
       </c>
       <c r="E4" t="n">
-        <v>-37.5</v>
+        <v>-38.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>18.33</v>
       </c>
       <c r="H4" t="n">
-        <v>-49.8</v>
+        <v>-50.4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>19.82</v>
       </c>
       <c r="K4" t="n">
-        <v>-45.7</v>
+        <v>-46.3</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>16.43</v>
       </c>
       <c r="N4" t="n">
-        <v>-55</v>
+        <v>-55.5</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>18.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>-50.5</v>
+        <v>-51.1</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86.76000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C5" t="n">
         <v>79.5</v>
@@ -800,7 +800,7 @@
         <v>54.12</v>
       </c>
       <c r="E5" t="n">
-        <v>-37.6</v>
+        <v>-38.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>49.44</v>
       </c>
       <c r="H5" t="n">
-        <v>-43</v>
+        <v>-44.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>50.99</v>
       </c>
       <c r="K5" t="n">
-        <v>-41.2</v>
+        <v>-42.3</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>47.51</v>
       </c>
       <c r="N5" t="n">
-        <v>-45.2</v>
+        <v>-46.3</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>49.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>-43.3</v>
+        <v>-44.3</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>70.06999999999999</v>
+        <v>71.91</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>75</v>
@@ -878,7 +878,7 @@
         <v>73.34999999999999</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -889,18 +889,18 @@
         <v>68.03</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>-2.9</v>
+        <v>-5.4</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>69.81</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.4</v>
+        <v>-2.9</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>65.84</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-6</v>
+        <v>-8.4</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -922,11 +922,11 @@
         <v>67.77</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-3.3</v>
+        <v>-5.8</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A/Set B/Set C/Set E; TRIM/SHORT under Set D</t>
+          <t>HOLD under Set A/Set C; TRIM/SHORT under Set B/Set D/Set E</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.05</v>
+        <v>6.16</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -956,7 +956,7 @@
         <v>2.76</v>
       </c>
       <c r="E7" t="n">
-        <v>-54.4</v>
+        <v>-55.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>2.31</v>
       </c>
       <c r="H7" t="n">
-        <v>-61.8</v>
+        <v>-62.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>2.46</v>
       </c>
       <c r="K7" t="n">
-        <v>-59.4</v>
+        <v>-60.1</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>2.13</v>
       </c>
       <c r="N7" t="n">
-        <v>-64.8</v>
+        <v>-65.5</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>2.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>-62.2</v>
+        <v>-62.8</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37.62</v>
+        <v>38.86</v>
       </c>
       <c r="C8" t="n">
         <v>51.5</v>
@@ -1034,7 +1034,7 @@
         <v>56.56</v>
       </c>
       <c r="E8" t="n">
-        <v>50.4</v>
+        <v>45.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>51.74</v>
       </c>
       <c r="H8" t="n">
-        <v>37.5</v>
+        <v>33.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>53.34</v>
       </c>
       <c r="K8" t="n">
-        <v>41.8</v>
+        <v>37.3</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>49.85</v>
       </c>
       <c r="N8" t="n">
-        <v>32.5</v>
+        <v>28.3</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>51.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>37.1</v>
+        <v>32.7</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14.96</v>
+        <v>15.08</v>
       </c>
       <c r="C9" t="n">
         <v>16.59</v>
@@ -1112,7 +1112,7 @@
         <v>14.09</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.8</v>
+        <v>-6.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>13.33</v>
       </c>
       <c r="H9" t="n">
-        <v>-10.9</v>
+        <v>-11.6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>13.58</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.9</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>13</v>
       </c>
       <c r="N9" t="n">
-        <v>-13.1</v>
+        <v>-13.8</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>13.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>-11.2</v>
+        <v>-11.9</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.5025</v>
+        <v>5.4152</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>7.13</v>
@@ -1190,7 +1190,7 @@
         <v>6.21</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12.8</v>
+        <v>14.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>3.3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>-40</v>
+        <v>-39.1</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>4.26</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-22.5</v>
+        <v>-21.3</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>2.05</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-62.8</v>
+        <v>-62.2</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>3.12</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-43.3</v>
+        <v>-42.4</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>12.718</v>
+        <v>12.6039</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>
@@ -1268,7 +1268,7 @@
         <v>13.14</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>10.23</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-19.6</v>
+        <v>-18.9</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>11.19</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-12</v>
+        <v>-11.2</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-29.2</v>
+        <v>-28.6</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>10.07</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-20.8</v>
+        <v>-20.1</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.89</v>
+        <v>18.45</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -566,7 +566,7 @@
         <v>13.1</v>
       </c>
       <c r="E2" t="n">
-        <v>-26.8</v>
+        <v>-29</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         <v>11.24</v>
       </c>
       <c r="H2" t="n">
-        <v>-37.2</v>
+        <v>-39.1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         <v>11.86</v>
       </c>
       <c r="K2" t="n">
-        <v>-33.7</v>
+        <v>-35.7</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         <v>10.45</v>
       </c>
       <c r="N2" t="n">
-        <v>-41.6</v>
+        <v>-43.3</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         <v>11.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>-37.8</v>
+        <v>-39.7</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54.24</v>
+        <v>57.88</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
@@ -644,7 +644,7 @@
         <v>32.1</v>
       </c>
       <c r="E3" t="n">
-        <v>-40.8</v>
+        <v>-44.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         <v>26.08</v>
       </c>
       <c r="H3" t="n">
-        <v>-51.9</v>
+        <v>-54.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>28.08</v>
       </c>
       <c r="K3" t="n">
-        <v>-48.2</v>
+        <v>-51.5</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>23.54</v>
       </c>
       <c r="N3" t="n">
-        <v>-56.6</v>
+        <v>-59.3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>25.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>-52.5</v>
+        <v>-55.5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.93</v>
+        <v>39.29</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
@@ -722,7 +722,7 @@
         <v>22.8</v>
       </c>
       <c r="E4" t="n">
-        <v>-38.3</v>
+        <v>-42</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>18.33</v>
       </c>
       <c r="H4" t="n">
-        <v>-50.4</v>
+        <v>-53.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>19.82</v>
       </c>
       <c r="K4" t="n">
-        <v>-46.3</v>
+        <v>-49.6</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>16.43</v>
       </c>
       <c r="N4" t="n">
-        <v>-55.5</v>
+        <v>-58.2</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>18.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>-51.1</v>
+        <v>-54</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>88.40000000000001</v>
+        <v>92.28</v>
       </c>
       <c r="C5" t="n">
         <v>79.5</v>
@@ -800,7 +800,7 @@
         <v>54.12</v>
       </c>
       <c r="E5" t="n">
-        <v>-38.8</v>
+        <v>-41.4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>49.44</v>
       </c>
       <c r="H5" t="n">
-        <v>-44.1</v>
+        <v>-46.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>50.99</v>
       </c>
       <c r="K5" t="n">
-        <v>-42.3</v>
+        <v>-44.7</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>47.51</v>
       </c>
       <c r="N5" t="n">
-        <v>-46.3</v>
+        <v>-48.5</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>49.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>-44.3</v>
+        <v>-46.7</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>71.91</v>
+        <v>75.81</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>75</v>
@@ -878,7 +878,7 @@
         <v>73.34999999999999</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>-3.2</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>68.03</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>-5.4</v>
+        <v>-10.3</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -900,18 +900,18 @@
         <v>69.81</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-2.9</v>
+        <v>-7.9</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
         <v>65.84</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-8.4</v>
+        <v>-13.1</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>67.77</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-5.8</v>
+        <v>-10.6</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A/Set C; TRIM/SHORT under Set B/Set D/Set E</t>
+          <t>HOLD under Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.16</v>
+        <v>6.45</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -956,7 +956,7 @@
         <v>2.76</v>
       </c>
       <c r="E7" t="n">
-        <v>-55.2</v>
+        <v>-57.3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>2.31</v>
       </c>
       <c r="H7" t="n">
-        <v>-62.5</v>
+        <v>-64.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>2.46</v>
       </c>
       <c r="K7" t="n">
-        <v>-60.1</v>
+        <v>-61.9</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>2.13</v>
       </c>
       <c r="N7" t="n">
-        <v>-65.5</v>
+        <v>-67</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>2.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>-62.8</v>
+        <v>-64.5</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38.86</v>
+        <v>39.4</v>
       </c>
       <c r="C8" t="n">
         <v>51.5</v>
@@ -1034,7 +1034,7 @@
         <v>56.56</v>
       </c>
       <c r="E8" t="n">
-        <v>45.6</v>
+        <v>43.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>51.74</v>
       </c>
       <c r="H8" t="n">
-        <v>33.1</v>
+        <v>31.3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>53.34</v>
       </c>
       <c r="K8" t="n">
-        <v>37.3</v>
+        <v>35.4</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>49.85</v>
       </c>
       <c r="N8" t="n">
-        <v>28.3</v>
+        <v>26.5</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>51.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>32.7</v>
+        <v>30.9</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1103,16 +1103,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.08</v>
+        <v>15.74</v>
       </c>
       <c r="C9" t="n">
         <v>16.59</v>
       </c>
       <c r="D9" t="n">
-        <v>14.09</v>
+        <v>13.99</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.5</v>
+        <v>-11.1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>13.33</v>
+        <v>13.22</v>
       </c>
       <c r="H9" t="n">
-        <v>-11.6</v>
+        <v>-16</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13.58</v>
+        <v>13.47</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.9</v>
+        <v>-14.4</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13</v>
+        <v>12.89</v>
       </c>
       <c r="N9" t="n">
-        <v>-13.8</v>
+        <v>-18.1</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>13.28</v>
+        <v>13.17</v>
       </c>
       <c r="Q9" t="n">
-        <v>-11.9</v>
+        <v>-16.3</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.4152</v>
+        <v>5.7234</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>7.13</v>
@@ -1190,7 +1190,7 @@
         <v>6.21</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14.6</v>
+        <v>8.4</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>3.3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>-39.1</v>
+        <v>-42.4</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>4.26</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-21.3</v>
+        <v>-25.5</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>2.05</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-62.2</v>
+        <v>-64.3</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>3.12</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-42.4</v>
+        <v>-45.5</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>12.6039</v>
+        <v>13.0112</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>
@@ -1268,7 +1268,7 @@
         <v>13.14</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>10.23</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-18.9</v>
+        <v>-21.4</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>11.19</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-11.2</v>
+        <v>-14</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-28.6</v>
+        <v>-30.8</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>10.07</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-20.1</v>
+        <v>-22.6</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -1109,10 +1109,10 @@
         <v>16.59</v>
       </c>
       <c r="D9" t="n">
-        <v>13.99</v>
+        <v>14.05</v>
       </c>
       <c r="E9" t="n">
-        <v>-11.1</v>
+        <v>-10.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>13.22</v>
+        <v>13.28</v>
       </c>
       <c r="H9" t="n">
-        <v>-16</v>
+        <v>-15.6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13.47</v>
+        <v>13.54</v>
       </c>
       <c r="K9" t="n">
-        <v>-14.4</v>
+        <v>-14</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>12.89</v>
+        <v>12.96</v>
       </c>
       <c r="N9" t="n">
-        <v>-18.1</v>
+        <v>-17.7</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>13.17</v>
+        <v>13.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>-16.3</v>
+        <v>-15.9</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -423,15 +423,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -444,8 +444,11 @@
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,85 +469,100 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Crude Set A' PW FV</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Crude Set A' EV %</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Crude Set A' position</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Crude Set A PW FV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Crude Set A EV %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Crude Set A position</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Crude Set B PW FV</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Crude Set B EV %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Crude Set B position</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Crude Set C PW FV</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Crude Set C EV %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Crude Set C position</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Crude Set D PW FV</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Crude Set D EV %</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Crude Set D position</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Crude Set E PW FV</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Crude Set E EV %</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Crude Set E position</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>robustness</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -557,13 +575,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.45</v>
+        <v>18.665</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>13.1</v>
+        <v>13.24</v>
       </c>
       <c r="E2" t="n">
         <v>-29</v>
@@ -574,57 +592,68 @@
         </is>
       </c>
       <c r="G2" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-29.8</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>11.24</v>
       </c>
-      <c r="H2" t="n">
-        <v>-39.1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
+        <v>-39.8</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>11.86</v>
       </c>
-      <c r="K2" t="n">
-        <v>-35.7</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
+        <v>-36.5</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
         <v>10.45</v>
       </c>
-      <c r="N2" t="n">
-        <v>-43.3</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
+        <v>-44</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
         <v>11.13</v>
       </c>
-      <c r="Q2" t="n">
-        <v>-39.7</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="n">
+        <v>-40.3</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all 5 weight sets</t>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 6 weight sets</t>
         </is>
       </c>
     </row>
@@ -635,74 +664,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57.88</v>
+        <v>60.48</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
       </c>
       <c r="D3" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-46.2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>32.1</v>
       </c>
-      <c r="E3" t="n">
-        <v>-44.5</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
+        <v>-46.9</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>26.08</v>
       </c>
-      <c r="H3" t="n">
-        <v>-54.9</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>-56.9</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>28.08</v>
       </c>
-      <c r="K3" t="n">
-        <v>-51.5</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
+        <v>-53.6</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
         <v>23.54</v>
       </c>
-      <c r="N3" t="n">
-        <v>-59.3</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
+        <v>-61.1</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
         <v>25.74</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-55.5</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="n">
+        <v>-57.4</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all 5 weight sets</t>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 6 weight sets</t>
         </is>
       </c>
     </row>
@@ -713,74 +753,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.29</v>
+        <v>39.34</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
       </c>
       <c r="D4" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-41.2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>22.8</v>
       </c>
-      <c r="E4" t="n">
+      <c r="H4" t="n">
         <v>-42</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>18.33</v>
       </c>
-      <c r="H4" t="n">
-        <v>-53.3</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>-53.4</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
         <v>19.82</v>
       </c>
-      <c r="K4" t="n">
+      <c r="N4" t="n">
         <v>-49.6</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
         <v>16.43</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>-58.2</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
         <v>18.07</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-54</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="n">
+        <v>-54.1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all 5 weight sets</t>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 6 weight sets</t>
         </is>
       </c>
     </row>
@@ -791,152 +842,174 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>92.28</v>
+        <v>96.13</v>
       </c>
       <c r="C5" t="n">
         <v>79.5</v>
       </c>
       <c r="D5" t="n">
+        <v>54.46</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-43.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>54.12</v>
       </c>
-      <c r="E5" t="n">
-        <v>-41.4</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>-43.7</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>49.44</v>
       </c>
-      <c r="H5" t="n">
-        <v>-46.4</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
+        <v>-48.6</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>50.99</v>
       </c>
-      <c r="K5" t="n">
-        <v>-44.7</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
+        <v>-47</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
         <v>47.51</v>
       </c>
-      <c r="N5" t="n">
-        <v>-48.5</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
+        <v>-50.6</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
         <v>49.21</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-46.7</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="n">
+        <v>-48.8</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all 5 weight sets</t>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 6 weight sets</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>TNK</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="C6" s="2" t="n">
+      <c r="B6" t="n">
+        <v>79.955</v>
+      </c>
+      <c r="C6" t="n">
         <v>75</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
+        <v>73.69</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>73.34999999999999</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>68.03</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
+      <c r="K6" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
         <v>69.81</v>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
+      <c r="N6" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
         <v>65.84</v>
       </c>
-      <c r="N6" s="2" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="n">
+      <c r="Q6" t="n">
+        <v>-17.7</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
         <v>67.77</v>
       </c>
-      <c r="Q6" s="2" t="n">
-        <v>-10.6</v>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>WEIGHT-DRIVEN</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD under Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
+      <c r="T6" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 6 weight sets</t>
         </is>
       </c>
     </row>
@@ -947,74 +1020,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.45</v>
+        <v>6.525</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-57.2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>2.76</v>
       </c>
-      <c r="E7" t="n">
-        <v>-57.3</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>-57.7</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>2.31</v>
       </c>
-      <c r="H7" t="n">
-        <v>-64.2</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
+        <v>-64.59999999999999</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
         <v>2.46</v>
       </c>
-      <c r="K7" t="n">
-        <v>-61.9</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
+        <v>-62.3</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
         <v>2.13</v>
       </c>
-      <c r="N7" t="n">
-        <v>-67</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
+        <v>-67.40000000000001</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
         <v>2.29</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-64.5</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="n">
+        <v>-64.90000000000001</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all 5 weight sets</t>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 6 weight sets</t>
         </is>
       </c>
     </row>
@@ -1025,74 +1109,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39.4</v>
+        <v>40.23</v>
       </c>
       <c r="C8" t="n">
         <v>51.5</v>
       </c>
       <c r="D8" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="E8" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>56.56</v>
       </c>
-      <c r="E8" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>51.74</v>
       </c>
-      <c r="H8" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>53.34</v>
       </c>
-      <c r="K8" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="P8" t="n">
         <v>49.85</v>
       </c>
-      <c r="N8" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>51.56</v>
       </c>
-      <c r="Q8" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>position BUY across all 5 weight sets</t>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>position BUY across all 6 weight sets</t>
         </is>
       </c>
     </row>
@@ -1103,74 +1198,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.74</v>
+        <v>16.16</v>
       </c>
       <c r="C9" t="n">
         <v>16.59</v>
       </c>
       <c r="D9" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>14.05</v>
       </c>
-      <c r="E9" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>13.28</v>
       </c>
-      <c r="H9" t="n">
-        <v>-15.6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
+        <v>-17.8</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
         <v>13.54</v>
       </c>
-      <c r="K9" t="n">
-        <v>-14</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
         <v>12.96</v>
       </c>
-      <c r="N9" t="n">
-        <v>-17.7</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>-19.8</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
         <v>13.24</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-15.9</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all 5 weight sets</t>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 6 weight sets</t>
         </is>
       </c>
     </row>
@@ -1181,74 +1287,85 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.7234</v>
+        <v>5.9711</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>7.13</v>
       </c>
       <c r="D10" s="2" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>6.21</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>-42.4</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
+      <c r="K10" s="2" t="n">
+        <v>-44.8</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
         <v>4.26</v>
       </c>
-      <c r="K10" s="2" t="n">
-        <v>-25.5</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
+      <c r="N10" s="2" t="n">
+        <v>-28.6</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n">
         <v>2.05</v>
       </c>
-      <c r="N10" s="2" t="n">
-        <v>-64.3</v>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="n">
+      <c r="Q10" s="2" t="n">
+        <v>-65.7</v>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>3.12</v>
       </c>
-      <c r="Q10" s="2" t="n">
-        <v>-45.5</v>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="n">
+        <v>-47.7</v>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>WEIGHT-DRIVEN</t>
         </is>
       </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>BUY under Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>BUY under Set A'; HOLD under Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>
@@ -1259,74 +1376,85 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>13.0112</v>
+        <v>13.5056</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>
       </c>
       <c r="D11" s="2" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>13.14</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="J11" s="2" t="n">
         <v>10.23</v>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>-21.4</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n">
+      <c r="K11" s="2" t="n">
+        <v>-24.3</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
         <v>11.19</v>
       </c>
-      <c r="K11" s="2" t="n">
-        <v>-14</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
+      <c r="N11" s="2" t="n">
+        <v>-17.1</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="N11" s="2" t="n">
-        <v>-30.8</v>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="n">
+      <c r="Q11" s="2" t="n">
+        <v>-33.4</v>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="n">
         <v>10.07</v>
       </c>
-      <c r="Q11" s="2" t="n">
-        <v>-22.6</v>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="n">
+        <v>-25.5</v>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>WEIGHT-DRIVEN</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>HOLD under Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>HOLD under Set A'/Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -925,91 +925,91 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TNK</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="2" t="n">
         <v>79.955</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="D6" t="n">
-        <v>73.69</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>73.34999999999999</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>68.03</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-14.9</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>69.81</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-12.7</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>65.84</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-17.7</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>67.77</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-15.2</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>WEIGHT-ROBUST</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all 6 weight sets</t>
+      <c r="D6" s="2" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>72.88</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>68.70999999999999</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>70.73999999999999</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>HOLD under Set A'/Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.665</v>
+        <v>18.76</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -584,7 +584,7 @@
         <v>13.24</v>
       </c>
       <c r="E2" t="n">
-        <v>-29</v>
+        <v>-29.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         <v>13.1</v>
       </c>
       <c r="H2" t="n">
-        <v>-29.8</v>
+        <v>-30.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
         <v>11.24</v>
       </c>
       <c r="K2" t="n">
-        <v>-39.8</v>
+        <v>-40.1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         <v>11.86</v>
       </c>
       <c r="N2" t="n">
-        <v>-36.5</v>
+        <v>-36.8</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
         <v>10.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>-44</v>
+        <v>-44.3</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         <v>11.13</v>
       </c>
       <c r="T2" t="n">
-        <v>-40.3</v>
+        <v>-40.6</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.48</v>
+        <v>61.86</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
@@ -673,7 +673,7 @@
         <v>32.57</v>
       </c>
       <c r="E3" t="n">
-        <v>-46.2</v>
+        <v>-47.4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>32.1</v>
       </c>
       <c r="H3" t="n">
-        <v>-46.9</v>
+        <v>-48.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         <v>26.08</v>
       </c>
       <c r="K3" t="n">
-        <v>-56.9</v>
+        <v>-57.8</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>28.08</v>
       </c>
       <c r="N3" t="n">
-        <v>-53.6</v>
+        <v>-54.6</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>23.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>-61.1</v>
+        <v>-62</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>25.74</v>
       </c>
       <c r="T3" t="n">
-        <v>-57.4</v>
+        <v>-58.4</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.34</v>
+        <v>39.74</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
@@ -762,7 +762,7 @@
         <v>23.15</v>
       </c>
       <c r="E4" t="n">
-        <v>-41.2</v>
+        <v>-41.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>22.8</v>
       </c>
       <c r="H4" t="n">
-        <v>-42</v>
+        <v>-42.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>18.33</v>
       </c>
       <c r="K4" t="n">
-        <v>-53.4</v>
+        <v>-53.9</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>19.82</v>
       </c>
       <c r="N4" t="n">
-        <v>-49.6</v>
+        <v>-50.1</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>16.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>-58.2</v>
+        <v>-58.7</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>18.07</v>
       </c>
       <c r="T4" t="n">
-        <v>-54.1</v>
+        <v>-54.5</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>96.13</v>
+        <v>92.41</v>
       </c>
       <c r="C5" t="n">
         <v>79.5</v>
@@ -851,7 +851,7 @@
         <v>54.46</v>
       </c>
       <c r="E5" t="n">
-        <v>-43.3</v>
+        <v>-41.1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>54.12</v>
       </c>
       <c r="H5" t="n">
-        <v>-43.7</v>
+        <v>-41.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>49.44</v>
       </c>
       <c r="K5" t="n">
-        <v>-48.6</v>
+        <v>-46.5</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>50.99</v>
       </c>
       <c r="N5" t="n">
-        <v>-47</v>
+        <v>-44.8</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>47.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>-50.6</v>
+        <v>-48.6</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>49.21</v>
       </c>
       <c r="T5" t="n">
-        <v>-48.8</v>
+        <v>-46.8</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>79.955</v>
+        <v>77.25</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>75</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>76.95</v>
+        <v>73.69</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-3.8</v>
+        <v>-4.6</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -948,21 +948,21 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>76.59999999999999</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>-4.2</v>
+        <v>-5</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>71.01000000000001</v>
+        <v>68.03</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-11.2</v>
+        <v>-11.9</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>72.88</v>
+        <v>69.81</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-8.9</v>
+        <v>-9.6</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>68.70999999999999</v>
+        <v>65.84</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-14.1</v>
+        <v>-14.8</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="S6" s="2" t="n">
-        <v>70.73999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-11.5</v>
+        <v>-12.3</v>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A'/Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
+          <t>HOLD under Set A'; TRIM/SHORT under Set A/Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.525</v>
+        <v>6.46</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -1029,7 +1029,7 @@
         <v>2.79</v>
       </c>
       <c r="E7" t="n">
-        <v>-57.2</v>
+        <v>-56.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>2.76</v>
       </c>
       <c r="H7" t="n">
-        <v>-57.7</v>
+        <v>-57.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>2.31</v>
       </c>
       <c r="K7" t="n">
-        <v>-64.59999999999999</v>
+        <v>-64.2</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>2.46</v>
       </c>
       <c r="N7" t="n">
-        <v>-62.3</v>
+        <v>-62</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>2.13</v>
       </c>
       <c r="Q7" t="n">
-        <v>-67.40000000000001</v>
+        <v>-67.09999999999999</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>2.29</v>
       </c>
       <c r="T7" t="n">
-        <v>-64.90000000000001</v>
+        <v>-64.59999999999999</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>40.23</v>
+        <v>39.14</v>
       </c>
       <c r="C8" t="n">
         <v>51.5</v>
@@ -1118,7 +1118,7 @@
         <v>56.83</v>
       </c>
       <c r="E8" t="n">
-        <v>41.3</v>
+        <v>45.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>56.56</v>
       </c>
       <c r="H8" t="n">
-        <v>40.6</v>
+        <v>44.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>51.74</v>
       </c>
       <c r="K8" t="n">
-        <v>28.6</v>
+        <v>32.2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>53.34</v>
       </c>
       <c r="N8" t="n">
-        <v>32.6</v>
+        <v>36.3</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>49.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>23.9</v>
+        <v>27.4</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>51.56</v>
       </c>
       <c r="T8" t="n">
-        <v>28.2</v>
+        <v>31.7</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.16</v>
+        <v>16.29</v>
       </c>
       <c r="C9" t="n">
         <v>16.59</v>
@@ -1207,7 +1207,7 @@
         <v>14.11</v>
       </c>
       <c r="E9" t="n">
-        <v>-12.7</v>
+        <v>-13.4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>14.05</v>
       </c>
       <c r="H9" t="n">
-        <v>-13.1</v>
+        <v>-13.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>13.28</v>
       </c>
       <c r="K9" t="n">
-        <v>-17.8</v>
+        <v>-18.5</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>13.54</v>
       </c>
       <c r="N9" t="n">
-        <v>-16.2</v>
+        <v>-16.9</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>12.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>-19.8</v>
+        <v>-20.5</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>13.24</v>
       </c>
       <c r="T9" t="n">
-        <v>-18.1</v>
+        <v>-18.7</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.9711</v>
+        <v>6.407</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>7.13</v>
@@ -1296,18 +1296,18 @@
         <v>6.45</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8.1</v>
+        <v>0.7</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
         <v>6.21</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3.9</v>
+        <v>-3.1</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>3.3</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-44.8</v>
+        <v>-48.5</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>4.26</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-28.6</v>
+        <v>-33.5</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>2.05</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-65.7</v>
+        <v>-68.09999999999999</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>3.12</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-47.7</v>
+        <v>-51.3</v>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>BUY under Set A'; HOLD under Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
+          <t>HOLD under Set A'/Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>13.5056</v>
+        <v>13.9395</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>
@@ -1385,7 +1385,7 @@
         <v>13.38</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1396,18 +1396,18 @@
         <v>13.14</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-2.7</v>
+        <v>-5.7</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
         <v>10.23</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-24.3</v>
+        <v>-26.6</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>11.19</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-17.1</v>
+        <v>-19.7</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>9</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-33.4</v>
+        <v>-35.4</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>10.07</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>-25.5</v>
+        <v>-27.8</v>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A'/Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
+          <t>HOLD under Set A'; TRIM/SHORT under Set A/Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -937,10 +937,10 @@
         <v>75</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>73.69</v>
+        <v>79.87</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-4.6</v>
+        <v>3.4</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -948,43 +948,43 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>73.34999999999999</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>-5</v>
+        <v>2.9</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>68.03</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-11.9</v>
+        <v>-4.3</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>69.81</v>
+        <v>75.77</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-9.6</v>
+        <v>-1.9</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>65.84</v>
+        <v>71.59</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-14.8</v>
+        <v>-7.3</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -992,14 +992,14 @@
         </is>
       </c>
       <c r="S6" s="2" t="n">
-        <v>67.77</v>
+        <v>73.62</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-12.3</v>
+        <v>-4.7</v>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A'; TRIM/SHORT under Set A/Set B/Set C/Set D/Set E</t>
+          <t>HOLD under Set A'/Set A/Set B/Set C/Set E; TRIM/SHORT under Set D</t>
         </is>
       </c>
     </row>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -670,10 +670,10 @@
         <v>45</v>
       </c>
       <c r="D3" t="n">
-        <v>32.57</v>
+        <v>35.69</v>
       </c>
       <c r="E3" t="n">
-        <v>-47.4</v>
+        <v>-42.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>32.1</v>
+        <v>35.24</v>
       </c>
       <c r="H3" t="n">
-        <v>-48.1</v>
+        <v>-43</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>26.08</v>
+        <v>29.29</v>
       </c>
       <c r="K3" t="n">
-        <v>-57.8</v>
+        <v>-52.7</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>28.08</v>
+        <v>31.27</v>
       </c>
       <c r="N3" t="n">
-        <v>-54.6</v>
+        <v>-49.5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>23.54</v>
+        <v>26.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>-62</v>
+        <v>-56.7</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>25.74</v>
+        <v>28.96</v>
       </c>
       <c r="T3" t="n">
-        <v>-58.4</v>
+        <v>-53.2</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -581,10 +581,10 @@
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>13.24</v>
+        <v>13.51</v>
       </c>
       <c r="E2" t="n">
-        <v>-29.4</v>
+        <v>-28</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>13.1</v>
+        <v>13.37</v>
       </c>
       <c r="H2" t="n">
-        <v>-30.2</v>
+        <v>-28.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>11.24</v>
+        <v>11.55</v>
       </c>
       <c r="K2" t="n">
-        <v>-40.1</v>
+        <v>-38.4</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>11.86</v>
+        <v>12.15</v>
       </c>
       <c r="N2" t="n">
-        <v>-36.8</v>
+        <v>-35.2</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>10.45</v>
+        <v>10.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>-44.3</v>
+        <v>-42.5</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>11.13</v>
+        <v>11.45</v>
       </c>
       <c r="T2" t="n">
-        <v>-40.6</v>
+        <v>-39</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -581,10 +581,10 @@
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>13.51</v>
+        <v>14.48</v>
       </c>
       <c r="E2" t="n">
-        <v>-28</v>
+        <v>-22.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>13.37</v>
+        <v>14.33</v>
       </c>
       <c r="H2" t="n">
-        <v>-28.7</v>
+        <v>-23.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>11.55</v>
+        <v>12.41</v>
       </c>
       <c r="K2" t="n">
-        <v>-38.4</v>
+        <v>-33.8</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>12.15</v>
+        <v>13.05</v>
       </c>
       <c r="N2" t="n">
-        <v>-35.2</v>
+        <v>-30.4</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>10.78</v>
+        <v>11.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>-42.5</v>
+        <v>-38.2</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>11.45</v>
+        <v>12.3</v>
       </c>
       <c r="T2" t="n">
-        <v>-39</v>
+        <v>-34.4</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -670,10 +670,10 @@
         <v>45</v>
       </c>
       <c r="D3" t="n">
-        <v>35.69</v>
+        <v>37.31</v>
       </c>
       <c r="E3" t="n">
-        <v>-42.3</v>
+        <v>-39.7</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>35.24</v>
+        <v>36.84</v>
       </c>
       <c r="H3" t="n">
-        <v>-43</v>
+        <v>-40.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>29.29</v>
+        <v>30.72</v>
       </c>
       <c r="K3" t="n">
-        <v>-52.7</v>
+        <v>-50.3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>31.27</v>
+        <v>32.76</v>
       </c>
       <c r="N3" t="n">
-        <v>-49.5</v>
+        <v>-47</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>26.79</v>
+        <v>28.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>-56.7</v>
+        <v>-54.5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>28.96</v>
+        <v>30.39</v>
       </c>
       <c r="T3" t="n">
-        <v>-53.2</v>
+        <v>-50.9</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -759,10 +759,10 @@
         <v>30.5</v>
       </c>
       <c r="D4" t="n">
-        <v>23.15</v>
+        <v>24.22</v>
       </c>
       <c r="E4" t="n">
-        <v>-41.8</v>
+        <v>-39</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>22.8</v>
+        <v>23.86</v>
       </c>
       <c r="H4" t="n">
-        <v>-42.6</v>
+        <v>-39.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>18.33</v>
+        <v>19.28</v>
       </c>
       <c r="K4" t="n">
-        <v>-53.9</v>
+        <v>-51.5</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>19.82</v>
+        <v>20.81</v>
       </c>
       <c r="N4" t="n">
-        <v>-50.1</v>
+        <v>-47.6</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>16.43</v>
+        <v>17.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>-58.7</v>
+        <v>-56.4</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>18.07</v>
+        <v>19.02</v>
       </c>
       <c r="T4" t="n">
-        <v>-54.5</v>
+        <v>-52.1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -848,10 +848,10 @@
         <v>79.5</v>
       </c>
       <c r="D5" t="n">
-        <v>54.46</v>
+        <v>55.59</v>
       </c>
       <c r="E5" t="n">
-        <v>-41.1</v>
+        <v>-39.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>54.12</v>
+        <v>55.24</v>
       </c>
       <c r="H5" t="n">
-        <v>-41.4</v>
+        <v>-40.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>49.44</v>
+        <v>50.44</v>
       </c>
       <c r="K5" t="n">
-        <v>-46.5</v>
+        <v>-45.4</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>50.99</v>
+        <v>52.03</v>
       </c>
       <c r="N5" t="n">
-        <v>-44.8</v>
+        <v>-43.7</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>47.51</v>
+        <v>48.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>-48.6</v>
+        <v>-47.6</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>49.21</v>
+        <v>50.19</v>
       </c>
       <c r="T5" t="n">
-        <v>-46.8</v>
+        <v>-45.7</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
         <v>51.5</v>
       </c>
       <c r="D8" t="n">
-        <v>56.83</v>
+        <v>57.16</v>
       </c>
       <c r="E8" t="n">
-        <v>45.2</v>
+        <v>46</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>56.56</v>
+        <v>56.89</v>
       </c>
       <c r="H8" t="n">
-        <v>44.5</v>
+        <v>45.3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>51.74</v>
+        <v>52.02</v>
       </c>
       <c r="K8" t="n">
-        <v>32.2</v>
+        <v>32.9</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>53.34</v>
+        <v>53.63</v>
       </c>
       <c r="N8" t="n">
-        <v>36.3</v>
+        <v>37</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>49.85</v>
+        <v>50.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.4</v>
+        <v>28</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>51.56</v>
+        <v>51.84</v>
       </c>
       <c r="T8" t="n">
-        <v>31.7</v>
+        <v>32.4</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         <v>16.59</v>
       </c>
       <c r="D9" t="n">
-        <v>14.11</v>
+        <v>13.86</v>
       </c>
       <c r="E9" t="n">
-        <v>-13.4</v>
+        <v>-14.9</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>14.05</v>
+        <v>13.8</v>
       </c>
       <c r="H9" t="n">
-        <v>-13.8</v>
+        <v>-15.3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13.28</v>
+        <v>13.03</v>
       </c>
       <c r="K9" t="n">
-        <v>-18.5</v>
+        <v>-20</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13.54</v>
+        <v>13.29</v>
       </c>
       <c r="N9" t="n">
-        <v>-16.9</v>
+        <v>-18.4</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>12.96</v>
+        <v>12.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>-20.5</v>
+        <v>-22</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>13.24</v>
+        <v>12.99</v>
       </c>
       <c r="T9" t="n">
-        <v>-18.7</v>
+        <v>-20.3</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1293,10 +1293,10 @@
         <v>7.13</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>6.21</v>
+        <v>6.24</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>-3.1</v>
+        <v>-2.6</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-48.5</v>
+        <v>-48</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4.26</v>
+        <v>4.3</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-33.5</v>
+        <v>-32.9</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-68.09999999999999</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="S10" s="2" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-51.3</v>
+        <v>-50.8</v>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
         <v>18.9</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>13.38</v>
+        <v>13.39</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-4</v>
+        <v>-3.9</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>13.14</v>
+        <v>13.16</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-5.7</v>
+        <v>-5.6</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>10.23</v>
+        <v>10.24</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-26.6</v>
+        <v>-26.5</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>11.19</v>
+        <v>11.2</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-19.7</v>
+        <v>-19.6</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>9</v>
+        <v>9.02</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-35.4</v>
+        <v>-35.3</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="S11" s="2" t="n">
-        <v>10.07</v>
+        <v>10.08</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>-27.8</v>
+        <v>-27.7</v>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -581,54 +581,54 @@
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>14.48</v>
+        <v>15.88</v>
       </c>
       <c r="E2" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-25.9</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="N2" t="n">
         <v>-22.8</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-23.6</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>12.41</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-33.8</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-30.4</v>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>11.6</v>
+        <v>13.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>-38.2</v>
+        <v>-30.3</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>12.3</v>
+        <v>13.76</v>
       </c>
       <c r="T2" t="n">
-        <v>-34.4</v>
+        <v>-26.7</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -670,10 +670,10 @@
         <v>45</v>
       </c>
       <c r="D3" t="n">
-        <v>37.31</v>
+        <v>41.44</v>
       </c>
       <c r="E3" t="n">
-        <v>-39.7</v>
+        <v>-33</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>36.84</v>
+        <v>40.83</v>
       </c>
       <c r="H3" t="n">
-        <v>-40.4</v>
+        <v>-34</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>30.72</v>
+        <v>35.1</v>
       </c>
       <c r="K3" t="n">
-        <v>-50.3</v>
+        <v>-43.3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>32.76</v>
+        <v>37</v>
       </c>
       <c r="N3" t="n">
-        <v>-47</v>
+        <v>-40.2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>28.15</v>
+        <v>32.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>-54.5</v>
+        <v>-47.5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>30.39</v>
+        <v>34.66</v>
       </c>
       <c r="T3" t="n">
-        <v>-50.9</v>
+        <v>-44</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -759,65 +759,65 @@
         <v>30.5</v>
       </c>
       <c r="D4" t="n">
-        <v>24.22</v>
+        <v>27.57</v>
       </c>
       <c r="E4" t="n">
+        <v>-30.6</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-31.8</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-42.6</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="N4" t="n">
         <v>-39</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>23.86</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-39.9</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>19.28</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-51.5</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>20.81</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-47.6</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-56.4</v>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>19.02</v>
+        <v>22.46</v>
       </c>
       <c r="T4" t="n">
-        <v>-52.1</v>
+        <v>-43.5</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -848,10 +848,10 @@
         <v>79.5</v>
       </c>
       <c r="D5" t="n">
-        <v>55.59</v>
+        <v>59.39</v>
       </c>
       <c r="E5" t="n">
-        <v>-39.8</v>
+        <v>-35.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>55.24</v>
+        <v>58.96</v>
       </c>
       <c r="H5" t="n">
-        <v>-40.2</v>
+        <v>-36.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>50.44</v>
+        <v>54.49</v>
       </c>
       <c r="K5" t="n">
-        <v>-45.4</v>
+        <v>-41</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>52.03</v>
+        <v>55.97</v>
       </c>
       <c r="N5" t="n">
-        <v>-43.7</v>
+        <v>-39.4</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>48.45</v>
+        <v>52.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>-47.6</v>
+        <v>-43.2</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>50.19</v>
+        <v>54.18</v>
       </c>
       <c r="T5" t="n">
-        <v>-45.7</v>
+        <v>-41.4</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -937,71 +937,71 @@
         <v>75</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>79.87</v>
+        <v>83.72</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>78.06999999999999</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>79.51000000000001</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="n">
+        <v>79.79000000000001</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="n">
+        <v>75.77</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n">
-        <v>75.77</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="n">
+        <v>77.70999999999999</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="P6" s="2" t="n">
-        <v>71.59</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>73.62</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
           <t>WEIGHT-DRIVEN</t>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A'/Set A/Set B/Set C/Set E; TRIM/SHORT under Set D</t>
+          <t>BUY under Set A'/Set A; HOLD under Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>
@@ -1026,10 +1026,10 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>2.79</v>
+        <v>3.05</v>
       </c>
       <c r="E7" t="n">
-        <v>-56.8</v>
+        <v>-52.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2.76</v>
+        <v>3.01</v>
       </c>
       <c r="H7" t="n">
-        <v>-57.3</v>
+        <v>-53.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2.31</v>
+        <v>2.59</v>
       </c>
       <c r="K7" t="n">
-        <v>-64.2</v>
+        <v>-59.9</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2.46</v>
+        <v>2.73</v>
       </c>
       <c r="N7" t="n">
-        <v>-62</v>
+        <v>-57.7</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>-67.09999999999999</v>
+        <v>-62.7</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>2.29</v>
+        <v>2.57</v>
       </c>
       <c r="T7" t="n">
-        <v>-64.59999999999999</v>
+        <v>-60.3</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
         <v>51.5</v>
       </c>
       <c r="D8" t="n">
-        <v>57.16</v>
+        <v>62.47</v>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>59.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>56.89</v>
+        <v>62.05</v>
       </c>
       <c r="H8" t="n">
-        <v>45.3</v>
+        <v>58.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>52.02</v>
+        <v>57.72</v>
       </c>
       <c r="K8" t="n">
-        <v>32.9</v>
+        <v>47.5</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>53.63</v>
+        <v>59.15</v>
       </c>
       <c r="N8" t="n">
-        <v>37</v>
+        <v>51.1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>50.11</v>
+        <v>55.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>42.6</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>51.84</v>
+        <v>57.42</v>
       </c>
       <c r="T8" t="n">
-        <v>32.4</v>
+        <v>46.7</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         <v>16.59</v>
       </c>
       <c r="D9" t="n">
-        <v>13.86</v>
+        <v>14.38</v>
       </c>
       <c r="E9" t="n">
-        <v>-14.9</v>
+        <v>-11.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="H9" t="n">
-        <v>-15.3</v>
+        <v>-12.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13.03</v>
+        <v>13.58</v>
       </c>
       <c r="K9" t="n">
-        <v>-20</v>
+        <v>-16.6</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13.29</v>
+        <v>13.82</v>
       </c>
       <c r="N9" t="n">
-        <v>-18.4</v>
+        <v>-15.2</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>12.7</v>
+        <v>13.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>-22</v>
+        <v>-18.7</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>12.99</v>
+        <v>13.52</v>
       </c>
       <c r="T9" t="n">
-        <v>-20.3</v>
+        <v>-17</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1293,54 +1293,54 @@
         <v>7.13</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6.49</v>
+        <v>9.33</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.3</v>
+        <v>45.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-48</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
       <c r="M10" s="2" t="n">
-        <v>4.3</v>
+        <v>7.19</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-32.9</v>
+        <v>12.2</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>2.08</v>
+        <v>5.01</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-67.59999999999999</v>
+        <v>-21.9</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="S10" s="2" t="n">
-        <v>3.15</v>
+        <v>6.05</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-50.8</v>
+        <v>-5.6</v>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A'/Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
+          <t>BUY under Set A'/Set A/Set C; HOLD under Set B; TRIM/SHORT under Set D/Set E</t>
         </is>
       </c>
     </row>
@@ -1382,54 +1382,54 @@
         <v>18.9</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>13.39</v>
+        <v>15.88</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-3.9</v>
+        <v>13.9</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>13.16</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>-26.5</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>-19.6</v>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="n">
-        <v>9.02</v>
+        <v>11.62</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-35.3</v>
+        <v>-16.6</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="S11" s="2" t="n">
-        <v>10.08</v>
+        <v>12.65</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>-27.7</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A'; TRIM/SHORT under Set A/Set B/Set C/Set D/Set E</t>
+          <t>BUY under Set A'/Set A; TRIM/SHORT under Set B/Set D/Set E; HOLD under Set C</t>
         </is>
       </c>
     </row>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -427,7 +427,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.76</v>
+        <v>18.72</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -584,7 +584,7 @@
         <v>15.88</v>
       </c>
       <c r="E2" t="n">
-        <v>-15.4</v>
+        <v>-15.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         <v>15.67</v>
       </c>
       <c r="H2" t="n">
-        <v>-16.5</v>
+        <v>-16.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
         <v>13.91</v>
       </c>
       <c r="K2" t="n">
-        <v>-25.9</v>
+        <v>-25.7</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         <v>14.49</v>
       </c>
       <c r="N2" t="n">
-        <v>-22.8</v>
+        <v>-22.6</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
         <v>13.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>-30.3</v>
+        <v>-30.1</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         <v>13.76</v>
       </c>
       <c r="T2" t="n">
-        <v>-26.7</v>
+        <v>-26.5</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.86</v>
+        <v>62.88</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
@@ -673,7 +673,7 @@
         <v>41.44</v>
       </c>
       <c r="E3" t="n">
-        <v>-33</v>
+        <v>-34.1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>40.83</v>
       </c>
       <c r="H3" t="n">
-        <v>-34</v>
+        <v>-35.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         <v>35.1</v>
       </c>
       <c r="K3" t="n">
-        <v>-43.3</v>
+        <v>-44.2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>37</v>
       </c>
       <c r="N3" t="n">
-        <v>-40.2</v>
+        <v>-41.2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>32.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>-47.5</v>
+        <v>-48.3</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>34.66</v>
       </c>
       <c r="T3" t="n">
-        <v>-44</v>
+        <v>-44.9</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.74</v>
+        <v>39.57</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
@@ -762,7 +762,7 @@
         <v>27.57</v>
       </c>
       <c r="E4" t="n">
-        <v>-30.6</v>
+        <v>-30.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>27.1</v>
       </c>
       <c r="H4" t="n">
-        <v>-31.8</v>
+        <v>-31.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>22.81</v>
       </c>
       <c r="K4" t="n">
-        <v>-42.6</v>
+        <v>-42.4</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>24.24</v>
       </c>
       <c r="N4" t="n">
-        <v>-39</v>
+        <v>-38.8</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>20.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>-47.6</v>
+        <v>-47.4</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>22.46</v>
       </c>
       <c r="T4" t="n">
-        <v>-43.5</v>
+        <v>-43.2</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>92.41</v>
+        <v>92.38</v>
       </c>
       <c r="C5" t="n">
         <v>79.5</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>77.25</v>
+        <v>80.89</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>75</v>
@@ -940,29 +940,29 @@
         <v>83.72</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8.4</v>
+        <v>3.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
         <v>83.25</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>7.8</v>
+        <v>2.9</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>78.06999999999999</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1.1</v>
+        <v>-3.5</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>79.79000000000001</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3.3</v>
+        <v>-1.4</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -984,18 +984,18 @@
         <v>75.77</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-1.9</v>
+        <v>-6.3</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="S6" s="2" t="n">
         <v>77.70999999999999</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.6</v>
+        <v>-3.9</v>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>BUY under Set A'/Set A; HOLD under Set B/Set C/Set D/Set E</t>
+          <t>HOLD under Set A'/Set A/Set B/Set C/Set E; TRIM/SHORT under Set D</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.46</v>
+        <v>6.44</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -1029,7 +1029,7 @@
         <v>3.05</v>
       </c>
       <c r="E7" t="n">
-        <v>-52.8</v>
+        <v>-52.6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>3.01</v>
       </c>
       <c r="H7" t="n">
-        <v>-53.4</v>
+        <v>-53.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>2.59</v>
       </c>
       <c r="K7" t="n">
-        <v>-59.9</v>
+        <v>-59.7</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>2.73</v>
       </c>
       <c r="N7" t="n">
-        <v>-57.7</v>
+        <v>-57.6</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>2.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>-62.7</v>
+        <v>-62.6</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>2.57</v>
       </c>
       <c r="T7" t="n">
-        <v>-60.3</v>
+        <v>-60.2</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39.14</v>
+        <v>39.31</v>
       </c>
       <c r="C8" t="n">
         <v>51.5</v>
@@ -1118,7 +1118,7 @@
         <v>62.47</v>
       </c>
       <c r="E8" t="n">
-        <v>59.6</v>
+        <v>58.9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>62.05</v>
       </c>
       <c r="H8" t="n">
-        <v>58.5</v>
+        <v>57.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>57.72</v>
       </c>
       <c r="K8" t="n">
-        <v>47.5</v>
+        <v>46.8</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>59.15</v>
       </c>
       <c r="N8" t="n">
-        <v>51.1</v>
+        <v>50.5</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>55.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>42.6</v>
+        <v>42</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>57.42</v>
       </c>
       <c r="T8" t="n">
-        <v>46.7</v>
+        <v>46.1</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.29</v>
+        <v>16.75</v>
       </c>
       <c r="C9" t="n">
         <v>16.59</v>
@@ -1207,7 +1207,7 @@
         <v>14.38</v>
       </c>
       <c r="E9" t="n">
-        <v>-11.7</v>
+        <v>-14.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>14.3</v>
       </c>
       <c r="H9" t="n">
-        <v>-12.2</v>
+        <v>-14.6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>13.58</v>
       </c>
       <c r="K9" t="n">
-        <v>-16.6</v>
+        <v>-18.9</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>13.82</v>
       </c>
       <c r="N9" t="n">
-        <v>-15.2</v>
+        <v>-17.5</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>13.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>-18.7</v>
+        <v>-20.9</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>13.52</v>
       </c>
       <c r="T9" t="n">
-        <v>-17</v>
+        <v>-19.3</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6.407</v>
+        <v>6.2576</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>7.13</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9.33</v>
+        <v>10.13</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>45.6</v>
+        <v>61.8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>8.98</v>
+        <v>9.77</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>40.1</v>
+        <v>56.1</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1315,21 +1315,21 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>6.3</v>
+        <v>7.07</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-1.6</v>
+        <v>13</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7.19</v>
+        <v>7.97</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>12.2</v>
+        <v>27.3</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>5.01</v>
+        <v>5.77</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-21.9</v>
+        <v>-7.9</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1348,14 +1348,14 @@
         </is>
       </c>
       <c r="S10" s="2" t="n">
-        <v>6.05</v>
+        <v>6.82</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-5.6</v>
+        <v>8.9</v>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>BUY under Set A'/Set A/Set C; HOLD under Set B; TRIM/SHORT under Set D/Set E</t>
+          <t>BUY under Set A'/Set A/Set B/Set C/Set E; TRIM/SHORT under Set D</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>13.9395</v>
+        <v>14.306</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>
@@ -1385,7 +1385,7 @@
         <v>15.88</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13.9</v>
+        <v>11</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>15.56</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>11.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>12.87</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-7.7</v>
+        <v>-10</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>13.76</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-1.3</v>
+        <v>-3.8</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>11.62</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-16.6</v>
+        <v>-18.8</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>12.65</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>-9.300000000000001</v>
+        <v>-11.6</v>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -423,18 +423,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
@@ -447,8 +447,11 @@
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="22" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="40" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,100 +472,115 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Crude Set A'' PW FV</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Crude Set A'' EV %</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Crude Set A'' position</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Crude Set A' PW FV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Crude Set A' EV %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Crude Set A' position</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Crude Set A PW FV</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Crude Set A EV %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Crude Set A position</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Crude Set B PW FV</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Crude Set B EV %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Crude Set B position</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Crude Set C PW FV</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Crude Set C EV %</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Crude Set C position</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Crude Set D PW FV</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Crude Set D EV %</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Crude Set D position</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Crude Set E PW FV</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Crude Set E EV %</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Crude Set E position</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>robustness</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -575,85 +593,96 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.72</v>
+        <v>19.52</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
       </c>
       <c r="D2" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-18.2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>15.88</v>
       </c>
-      <c r="E2" t="n">
-        <v>-15.2</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
+        <v>-18.7</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>15.67</v>
       </c>
-      <c r="H2" t="n">
-        <v>-16.3</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>13.91</v>
       </c>
-      <c r="K2" t="n">
-        <v>-25.7</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
         <v>14.49</v>
       </c>
-      <c r="N2" t="n">
-        <v>-22.6</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
+        <v>-25.8</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
         <v>13.08</v>
       </c>
-      <c r="Q2" t="n">
-        <v>-30.1</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
+        <v>-33</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
         <v>13.76</v>
       </c>
-      <c r="T2" t="n">
-        <v>-26.5</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="n">
+        <v>-29.5</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all 6 weight sets</t>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 7 weight sets</t>
         </is>
       </c>
     </row>
@@ -664,85 +693,96 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62.88</v>
+        <v>60.29</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
       </c>
       <c r="D3" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-30.8</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>41.44</v>
       </c>
-      <c r="E3" t="n">
-        <v>-34.1</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
+        <v>-31.3</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>40.83</v>
       </c>
-      <c r="H3" t="n">
-        <v>-35.1</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>-32.3</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>35.1</v>
       </c>
-      <c r="K3" t="n">
-        <v>-44.2</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
+        <v>-41.8</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
         <v>37</v>
       </c>
-      <c r="N3" t="n">
-        <v>-41.2</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
+        <v>-38.6</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
         <v>32.49</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-48.3</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
+        <v>-46.1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
         <v>34.66</v>
       </c>
-      <c r="T3" t="n">
-        <v>-44.9</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="n">
+        <v>-42.5</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all 6 weight sets</t>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 7 weight sets</t>
         </is>
       </c>
     </row>
@@ -753,85 +793,96 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.57</v>
+        <v>41.21</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
       </c>
       <c r="D4" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-32.6</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>27.57</v>
       </c>
-      <c r="E4" t="n">
-        <v>-30.3</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>27.1</v>
       </c>
-      <c r="H4" t="n">
-        <v>-31.5</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>-34.2</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
         <v>22.81</v>
       </c>
-      <c r="K4" t="n">
-        <v>-42.4</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
+        <v>-44.6</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
         <v>24.24</v>
       </c>
-      <c r="N4" t="n">
-        <v>-38.8</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
+        <v>-41.2</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
         <v>20.82</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-47.4</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
+        <v>-49.5</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
         <v>22.46</v>
       </c>
-      <c r="T4" t="n">
-        <v>-43.2</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="n">
+        <v>-45.5</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all 6 weight sets</t>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 7 weight sets</t>
         </is>
       </c>
     </row>
@@ -842,85 +893,96 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>92.38</v>
+        <v>97.05</v>
       </c>
       <c r="C5" t="n">
         <v>79.5</v>
       </c>
       <c r="D5" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-38.6</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>59.39</v>
       </c>
-      <c r="E5" t="n">
-        <v>-35.7</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>-38.8</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>58.96</v>
       </c>
-      <c r="H5" t="n">
-        <v>-36.2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
+        <v>-39.3</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>54.49</v>
       </c>
-      <c r="K5" t="n">
-        <v>-41</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
+        <v>-43.9</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
         <v>55.97</v>
       </c>
-      <c r="N5" t="n">
-        <v>-39.4</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
+        <v>-42.3</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
         <v>52.51</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-43.2</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
+        <v>-45.9</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
         <v>54.18</v>
       </c>
-      <c r="T5" t="n">
-        <v>-41.4</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="n">
+        <v>-44.2</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all 6 weight sets</t>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 7 weight sets</t>
         </is>
       </c>
     </row>
@@ -931,57 +993,57 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>80.89</v>
+        <v>85.13</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>75</v>
       </c>
       <c r="D6" s="2" t="n">
+        <v>83.93000000000001</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>83.72</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="J6" s="2" t="n">
         <v>83.25</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="M6" s="2" t="n">
         <v>78.06999999999999</v>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
+      <c r="N6" s="2" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n">
         <v>79.79000000000001</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>75.77</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>-6.3</v>
@@ -992,24 +1054,35 @@
         </is>
       </c>
       <c r="S6" s="2" t="n">
+        <v>75.77</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>-11</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="n">
         <v>77.70999999999999</v>
       </c>
-      <c r="T6" s="2" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="W6" s="2" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>WEIGHT-DRIVEN</t>
         </is>
       </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD under Set A'/Set A/Set B/Set C/Set E; TRIM/SHORT under Set D</t>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>HOLD under Set A''/Set A'/Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>
@@ -1020,85 +1093,96 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.44</v>
+        <v>6.71</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-54.3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>3.05</v>
       </c>
-      <c r="E7" t="n">
-        <v>-52.6</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>-54.5</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>3.01</v>
       </c>
-      <c r="H7" t="n">
-        <v>-53.3</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
+        <v>-55.1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
         <v>2.59</v>
       </c>
-      <c r="K7" t="n">
-        <v>-59.7</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
+        <v>-61.4</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
         <v>2.73</v>
       </c>
-      <c r="N7" t="n">
-        <v>-57.6</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
+        <v>-59.3</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
         <v>2.41</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-62.6</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
+        <v>-64.09999999999999</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
         <v>2.57</v>
       </c>
-      <c r="T7" t="n">
-        <v>-60.2</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="n">
+        <v>-61.8</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all 6 weight sets</t>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 7 weight sets</t>
         </is>
       </c>
     </row>
@@ -1109,85 +1193,96 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39.31</v>
+        <v>41.45</v>
       </c>
       <c r="C8" t="n">
         <v>51.5</v>
       </c>
       <c r="D8" t="n">
+        <v>62.66</v>
+      </c>
+      <c r="E8" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>62.47</v>
       </c>
-      <c r="E8" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>62.05</v>
       </c>
-      <c r="H8" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>57.72</v>
       </c>
-      <c r="K8" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="P8" t="n">
         <v>59.15</v>
       </c>
-      <c r="N8" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>55.81</v>
       </c>
-      <c r="Q8" t="n">
-        <v>42</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
         <v>57.42</v>
       </c>
-      <c r="T8" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="W8" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>position BUY across all 6 weight sets</t>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>position BUY across all 7 weight sets</t>
         </is>
       </c>
     </row>
@@ -1198,85 +1293,96 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.75</v>
+        <v>17.24</v>
       </c>
       <c r="C9" t="n">
         <v>16.59</v>
       </c>
       <c r="D9" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>14.38</v>
       </c>
-      <c r="E9" t="n">
-        <v>-14.2</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>14.3</v>
       </c>
-      <c r="H9" t="n">
-        <v>-14.6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
+        <v>-17</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
         <v>13.58</v>
       </c>
-      <c r="K9" t="n">
-        <v>-18.9</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
         <v>13.82</v>
       </c>
-      <c r="N9" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>-19.8</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
         <v>13.25</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-20.9</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
+        <v>-23.1</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
         <v>13.52</v>
       </c>
-      <c r="T9" t="n">
-        <v>-19.3</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="n">
+        <v>-21.6</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>WEIGHT-ROBUST</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all 6 weight sets</t>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 7 weight sets</t>
         </is>
       </c>
     </row>
@@ -1287,85 +1393,96 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6.2576</v>
+        <v>6.7429</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>7.13</v>
       </c>
       <c r="D10" s="2" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>10.13</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="J10" s="2" t="n">
         <v>9.77</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="M10" s="2" t="n">
         <v>7.07</v>
       </c>
-      <c r="K10" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="n">
+      <c r="S10" s="2" t="n">
         <v>5.77</v>
       </c>
-      <c r="Q10" s="2" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="n">
+      <c r="T10" s="2" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="n">
         <v>6.82</v>
       </c>
-      <c r="T10" s="2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="W10" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>WEIGHT-DRIVEN</t>
         </is>
       </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>BUY under Set A'/Set A/Set B/Set C/Set E; TRIM/SHORT under Set D</t>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>BUY under Set A''/Set A'/Set A/Set C; HOLD under Set B/Set E; TRIM/SHORT under Set D</t>
         </is>
       </c>
     </row>
@@ -1376,85 +1493,96 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>14.306</v>
+        <v>14.6837</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>
       </c>
       <c r="D11" s="2" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>15.88</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="J11" s="2" t="n">
         <v>15.56</v>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="M11" s="2" t="n">
         <v>12.87</v>
       </c>
-      <c r="K11" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
+      <c r="N11" s="2" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="n">
         <v>13.76</v>
       </c>
-      <c r="N11" s="2" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="n">
+      <c r="Q11" s="2" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="n">
         <v>11.62</v>
       </c>
-      <c r="Q11" s="2" t="n">
-        <v>-18.8</v>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="n">
+      <c r="T11" s="2" t="n">
+        <v>-20.9</v>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="n">
         <v>12.65</v>
       </c>
-      <c r="T11" s="2" t="n">
-        <v>-11.6</v>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="W11" s="2" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
         <is>
           <t>WEIGHT-DRIVEN</t>
         </is>
       </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>BUY under Set A'/Set A; TRIM/SHORT under Set B/Set D/Set E; HOLD under Set C</t>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>BUY under Set A''/Set A'/Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.52</v>
+        <v>19.17</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -602,7 +602,7 @@
         <v>15.97</v>
       </c>
       <c r="E2" t="n">
-        <v>-18.2</v>
+        <v>-16.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         <v>15.88</v>
       </c>
       <c r="H2" t="n">
-        <v>-18.7</v>
+        <v>-17.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         <v>15.67</v>
       </c>
       <c r="K2" t="n">
-        <v>-19.7</v>
+        <v>-18.3</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         <v>13.91</v>
       </c>
       <c r="N2" t="n">
-        <v>-28.8</v>
+        <v>-27.5</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
         <v>14.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>-25.8</v>
+        <v>-24.4</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>13.08</v>
       </c>
       <c r="T2" t="n">
-        <v>-33</v>
+        <v>-31.8</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
         <v>13.76</v>
       </c>
       <c r="W2" t="n">
-        <v>-29.5</v>
+        <v>-28.2</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.29</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
@@ -702,7 +702,7 @@
         <v>41.71</v>
       </c>
       <c r="E3" t="n">
-        <v>-30.8</v>
+        <v>-35.9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>41.44</v>
       </c>
       <c r="H3" t="n">
-        <v>-31.3</v>
+        <v>-36.3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>40.83</v>
       </c>
       <c r="K3" t="n">
-        <v>-32.3</v>
+        <v>-37.2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>35.1</v>
       </c>
       <c r="N3" t="n">
-        <v>-41.8</v>
+        <v>-46</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>37</v>
       </c>
       <c r="Q3" t="n">
-        <v>-38.6</v>
+        <v>-43.1</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>32.49</v>
       </c>
       <c r="T3" t="n">
-        <v>-46.1</v>
+        <v>-50</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         <v>34.66</v>
       </c>
       <c r="W3" t="n">
-        <v>-42.5</v>
+        <v>-46.7</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.21</v>
+        <v>43.46</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
@@ -802,7 +802,7 @@
         <v>27.79</v>
       </c>
       <c r="E4" t="n">
-        <v>-32.6</v>
+        <v>-36.1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>27.57</v>
       </c>
       <c r="H4" t="n">
-        <v>-33.1</v>
+        <v>-36.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>27.1</v>
       </c>
       <c r="K4" t="n">
-        <v>-34.2</v>
+        <v>-37.7</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>22.81</v>
       </c>
       <c r="N4" t="n">
-        <v>-44.6</v>
+        <v>-47.5</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>24.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>-41.2</v>
+        <v>-44.2</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>20.82</v>
       </c>
       <c r="T4" t="n">
-        <v>-49.5</v>
+        <v>-52.1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>22.46</v>
       </c>
       <c r="W4" t="n">
-        <v>-45.5</v>
+        <v>-48.3</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>97.05</v>
+        <v>99.05</v>
       </c>
       <c r="C5" t="n">
         <v>79.5</v>
@@ -902,7 +902,7 @@
         <v>59.59</v>
       </c>
       <c r="E5" t="n">
-        <v>-38.6</v>
+        <v>-39.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>59.39</v>
       </c>
       <c r="H5" t="n">
-        <v>-38.8</v>
+        <v>-40</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>58.96</v>
       </c>
       <c r="K5" t="n">
-        <v>-39.3</v>
+        <v>-40.5</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>54.49</v>
       </c>
       <c r="N5" t="n">
-        <v>-43.9</v>
+        <v>-45</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>55.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>-42.3</v>
+        <v>-43.5</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>52.51</v>
       </c>
       <c r="T5" t="n">
-        <v>-45.9</v>
+        <v>-47</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>54.18</v>
       </c>
       <c r="W5" t="n">
-        <v>-44.2</v>
+        <v>-45.3</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -987,102 +987,102 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>TNK</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>85.13</v>
-      </c>
-      <c r="C6" s="2" t="n">
+      <c r="B6" t="n">
+        <v>90.03</v>
+      </c>
+      <c r="C6" t="n">
         <v>75</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
         <v>83.93000000000001</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
+      <c r="E6" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>83.72</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
+      <c r="H6" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>83.25</v>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
+      <c r="K6" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
         <v>78.06999999999999</v>
       </c>
-      <c r="N6" s="2" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="n">
+      <c r="N6" t="n">
+        <v>-13.3</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
         <v>79.79000000000001</v>
       </c>
-      <c r="Q6" s="2" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="n">
+      <c r="Q6" t="n">
+        <v>-11.4</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
         <v>75.77</v>
       </c>
-      <c r="T6" s="2" t="n">
-        <v>-11</v>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="n">
+      <c r="T6" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
         <v>77.70999999999999</v>
       </c>
-      <c r="W6" s="2" t="n">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>WEIGHT-DRIVEN</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD under Set A''/Set A'/Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
+      <c r="W6" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 7 weight sets</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.71</v>
+        <v>6.9</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -1102,7 +1102,7 @@
         <v>3.07</v>
       </c>
       <c r="E7" t="n">
-        <v>-54.3</v>
+        <v>-55.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>3.05</v>
       </c>
       <c r="H7" t="n">
-        <v>-54.5</v>
+        <v>-55.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>3.01</v>
       </c>
       <c r="K7" t="n">
-        <v>-55.1</v>
+        <v>-56.4</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>2.59</v>
       </c>
       <c r="N7" t="n">
-        <v>-61.4</v>
+        <v>-62.4</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>2.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>-59.3</v>
+        <v>-60.4</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>2.41</v>
       </c>
       <c r="T7" t="n">
-        <v>-64.09999999999999</v>
+        <v>-65.09999999999999</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>2.57</v>
       </c>
       <c r="W7" t="n">
-        <v>-61.8</v>
+        <v>-62.8</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41.45</v>
+        <v>42.27</v>
       </c>
       <c r="C8" t="n">
         <v>51.5</v>
@@ -1202,7 +1202,7 @@
         <v>62.66</v>
       </c>
       <c r="E8" t="n">
-        <v>51.2</v>
+        <v>48.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>62.47</v>
       </c>
       <c r="H8" t="n">
-        <v>50.7</v>
+        <v>47.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>62.05</v>
       </c>
       <c r="K8" t="n">
-        <v>49.7</v>
+        <v>46.8</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>57.72</v>
       </c>
       <c r="N8" t="n">
-        <v>39.3</v>
+        <v>36.5</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>59.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>42.7</v>
+        <v>39.9</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>55.81</v>
       </c>
       <c r="T8" t="n">
-        <v>34.6</v>
+        <v>32</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>57.42</v>
       </c>
       <c r="W8" t="n">
-        <v>38.5</v>
+        <v>35.9</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.24</v>
+        <v>18.17</v>
       </c>
       <c r="C9" t="n">
         <v>16.59</v>
@@ -1302,7 +1302,7 @@
         <v>14.41</v>
       </c>
       <c r="E9" t="n">
-        <v>-16.4</v>
+        <v>-20.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>14.38</v>
       </c>
       <c r="H9" t="n">
-        <v>-16.6</v>
+        <v>-20.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>14.3</v>
       </c>
       <c r="K9" t="n">
-        <v>-17</v>
+        <v>-21.3</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>13.58</v>
       </c>
       <c r="N9" t="n">
-        <v>-21.2</v>
+        <v>-25.3</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>13.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>-19.8</v>
+        <v>-24</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>13.25</v>
       </c>
       <c r="T9" t="n">
-        <v>-23.1</v>
+        <v>-27.1</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>13.52</v>
       </c>
       <c r="W9" t="n">
-        <v>-21.6</v>
+        <v>-25.6</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6.7429</v>
+        <v>6.32</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>7.13</v>
@@ -1402,7 +1402,7 @@
         <v>10.28</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>52.5</v>
+        <v>62.7</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>10.13</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>50.2</v>
+        <v>60.2</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>9.77</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>44.9</v>
+        <v>54.6</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
@@ -1435,18 +1435,18 @@
         <v>7.07</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>4.9</v>
+        <v>11.9</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
         <v>7.97</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>18.1</v>
+        <v>26</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>5.77</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-14.5</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
@@ -1468,11 +1468,11 @@
         <v>6.82</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>1.1</v>
+        <v>7.8</v>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>BUY under Set A''/Set A'/Set A/Set C; HOLD under Set B/Set E; TRIM/SHORT under Set D</t>
+          <t>BUY under Set A''/Set A'/Set A/Set B/Set C/Set E; TRIM/SHORT under Set D</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>14.6837</v>
+        <v>16.5334</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>
@@ -1502,40 +1502,40 @@
         <v>16.02</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>9.1</v>
+        <v>-3.1</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
         <v>15.88</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>8.1</v>
+        <v>-3.9</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
         <v>15.56</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>6</v>
+        <v>-5.9</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
         <v>12.87</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-12.3</v>
+        <v>-22.1</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>13.76</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-6.3</v>
+        <v>-16.8</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>11.62</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>-20.9</v>
+        <v>-29.7</v>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>12.65</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>-13.9</v>
+        <v>-23.5</v>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>BUY under Set A''/Set A'/Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
+          <t>HOLD under Set A''/Set A'; TRIM/SHORT under Set A/Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.17</v>
+        <v>19.66</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
@@ -602,7 +602,7 @@
         <v>15.97</v>
       </c>
       <c r="E2" t="n">
-        <v>-16.7</v>
+        <v>-18.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         <v>15.88</v>
       </c>
       <c r="H2" t="n">
-        <v>-17.2</v>
+        <v>-19.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         <v>15.67</v>
       </c>
       <c r="K2" t="n">
-        <v>-18.3</v>
+        <v>-20.3</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         <v>13.91</v>
       </c>
       <c r="N2" t="n">
-        <v>-27.5</v>
+        <v>-29.3</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
         <v>14.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>-24.4</v>
+        <v>-26.3</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>13.08</v>
       </c>
       <c r="T2" t="n">
-        <v>-31.8</v>
+        <v>-33.5</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
         <v>13.76</v>
       </c>
       <c r="W2" t="n">
-        <v>-28.2</v>
+        <v>-30</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.04000000000001</v>
+        <v>66.86</v>
       </c>
       <c r="C3" t="n">
         <v>45</v>
@@ -702,7 +702,7 @@
         <v>41.71</v>
       </c>
       <c r="E3" t="n">
-        <v>-35.9</v>
+        <v>-37.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>41.44</v>
       </c>
       <c r="H3" t="n">
-        <v>-36.3</v>
+        <v>-38</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>40.83</v>
       </c>
       <c r="K3" t="n">
-        <v>-37.2</v>
+        <v>-38.9</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>35.1</v>
       </c>
       <c r="N3" t="n">
-        <v>-46</v>
+        <v>-47.5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>37</v>
       </c>
       <c r="Q3" t="n">
-        <v>-43.1</v>
+        <v>-44.7</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>32.49</v>
       </c>
       <c r="T3" t="n">
-        <v>-50</v>
+        <v>-51.4</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         <v>34.66</v>
       </c>
       <c r="W3" t="n">
-        <v>-46.7</v>
+        <v>-48.2</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.46</v>
+        <v>44.19</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
@@ -802,7 +802,7 @@
         <v>27.79</v>
       </c>
       <c r="E4" t="n">
-        <v>-36.1</v>
+        <v>-37.1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>27.57</v>
       </c>
       <c r="H4" t="n">
-        <v>-36.6</v>
+        <v>-37.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>27.1</v>
       </c>
       <c r="K4" t="n">
-        <v>-37.7</v>
+        <v>-38.7</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>22.81</v>
       </c>
       <c r="N4" t="n">
-        <v>-47.5</v>
+        <v>-48.4</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>24.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>-44.2</v>
+        <v>-45.2</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>20.82</v>
       </c>
       <c r="T4" t="n">
-        <v>-52.1</v>
+        <v>-52.9</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>22.46</v>
       </c>
       <c r="W4" t="n">
-        <v>-48.3</v>
+        <v>-49.2</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>99.05</v>
+        <v>98.81</v>
       </c>
       <c r="C5" t="n">
         <v>79.5</v>
@@ -902,7 +902,7 @@
         <v>59.59</v>
       </c>
       <c r="E5" t="n">
-        <v>-39.8</v>
+        <v>-39.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>59.39</v>
       </c>
       <c r="H5" t="n">
-        <v>-40</v>
+        <v>-39.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>58.96</v>
       </c>
       <c r="K5" t="n">
-        <v>-40.5</v>
+        <v>-40.3</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>54.49</v>
       </c>
       <c r="N5" t="n">
-        <v>-45</v>
+        <v>-44.9</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>55.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>-43.5</v>
+        <v>-43.4</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>52.51</v>
       </c>
       <c r="T5" t="n">
-        <v>-47</v>
+        <v>-46.9</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>54.18</v>
       </c>
       <c r="W5" t="n">
-        <v>-45.3</v>
+        <v>-45.2</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>90.03</v>
+        <v>88.7</v>
       </c>
       <c r="C6" t="n">
         <v>75</v>
@@ -1002,7 +1002,7 @@
         <v>83.93000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.8</v>
+        <v>-5.4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>83.72</v>
       </c>
       <c r="H6" t="n">
-        <v>-7</v>
+        <v>-5.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>83.25</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.5</v>
+        <v>-6.1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>78.06999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-13.3</v>
+        <v>-12</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>79.79000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-11.4</v>
+        <v>-10</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>75.77</v>
       </c>
       <c r="T6" t="n">
-        <v>-15.8</v>
+        <v>-14.6</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>77.70999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>-13.7</v>
+        <v>-12.4</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.9</v>
+        <v>6.77</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -1102,7 +1102,7 @@
         <v>3.07</v>
       </c>
       <c r="E7" t="n">
-        <v>-55.5</v>
+        <v>-54.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>3.05</v>
       </c>
       <c r="H7" t="n">
-        <v>-55.8</v>
+        <v>-54.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>3.01</v>
       </c>
       <c r="K7" t="n">
-        <v>-56.4</v>
+        <v>-55.5</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>2.59</v>
       </c>
       <c r="N7" t="n">
-        <v>-62.4</v>
+        <v>-61.7</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>2.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>-60.4</v>
+        <v>-59.7</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>2.41</v>
       </c>
       <c r="T7" t="n">
-        <v>-65.09999999999999</v>
+        <v>-64.40000000000001</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>2.57</v>
       </c>
       <c r="W7" t="n">
-        <v>-62.8</v>
+        <v>-62.1</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>42.27</v>
+        <v>42.52</v>
       </c>
       <c r="C8" t="n">
         <v>51.5</v>
@@ -1202,7 +1202,7 @@
         <v>62.66</v>
       </c>
       <c r="E8" t="n">
-        <v>48.2</v>
+        <v>47.4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>62.47</v>
       </c>
       <c r="H8" t="n">
-        <v>47.8</v>
+        <v>46.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>62.05</v>
       </c>
       <c r="K8" t="n">
-        <v>46.8</v>
+        <v>45.9</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>57.72</v>
       </c>
       <c r="N8" t="n">
-        <v>36.5</v>
+        <v>35.7</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>59.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>39.9</v>
+        <v>39.1</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>55.81</v>
       </c>
       <c r="T8" t="n">
-        <v>32</v>
+        <v>31.2</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>57.42</v>
       </c>
       <c r="W8" t="n">
-        <v>35.9</v>
+        <v>35.1</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.17</v>
+        <v>18.35</v>
       </c>
       <c r="C9" t="n">
         <v>16.59</v>
@@ -1302,7 +1302,7 @@
         <v>14.41</v>
       </c>
       <c r="E9" t="n">
-        <v>-20.7</v>
+        <v>-21.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>14.38</v>
       </c>
       <c r="H9" t="n">
-        <v>-20.9</v>
+        <v>-21.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>14.3</v>
       </c>
       <c r="K9" t="n">
-        <v>-21.3</v>
+        <v>-22.1</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>13.58</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.3</v>
+        <v>-26</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>13.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>-24</v>
+        <v>-24.7</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>13.25</v>
       </c>
       <c r="T9" t="n">
-        <v>-27.1</v>
+        <v>-27.8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>13.52</v>
       </c>
       <c r="W9" t="n">
-        <v>-25.6</v>
+        <v>-26.3</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1387,102 +1387,102 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>BRUT</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="C10" s="2" t="n">
+      <c r="B10" t="n">
+        <v>4.9444</v>
+      </c>
+      <c r="C10" t="n">
         <v>7.13</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" t="n">
         <v>10.28</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" t="n">
+        <v>108</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" t="n">
         <v>10.13</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="H10" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" t="n">
         <v>9.77</v>
       </c>
-      <c r="K10" s="2" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="M10" t="n">
         <v>7.07</v>
       </c>
-      <c r="N10" s="2" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="N10" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="P10" t="n">
         <v>7.97</v>
       </c>
-      <c r="Q10" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="Q10" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="S10" s="2" t="n">
+      <c r="S10" t="n">
         <v>5.77</v>
       </c>
-      <c r="T10" s="2" t="n">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="n">
+      <c r="T10" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
         <v>6.82</v>
       </c>
-      <c r="W10" s="2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="X10" s="2" t="inlineStr">
+      <c r="W10" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>WEIGHT-DRIVEN</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>BUY under Set A''/Set A'/Set A/Set B/Set C/Set E; TRIM/SHORT under Set D</t>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>position BUY across all 7 weight sets</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>16.5334</v>
+        <v>16.4629</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>
@@ -1502,7 +1502,7 @@
         <v>16.02</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-3.1</v>
+        <v>-2.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>15.88</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-3.9</v>
+        <v>-3.5</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>15.56</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-5.9</v>
+        <v>-5.5</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>12.87</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-22.1</v>
+        <v>-21.8</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>13.76</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-16.8</v>
+        <v>-16.4</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>11.62</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>-29.7</v>
+        <v>-29.4</v>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>12.65</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>-23.5</v>
+        <v>-23.2</v>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -1387,102 +1387,102 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>BRUT</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="2" t="n">
         <v>4.9444</v>
       </c>
-      <c r="C10" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="D10" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="E10" t="n">
-        <v>108</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="H10" t="n">
-        <v>104.8</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="K10" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="N10" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="T10" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="W10" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>WEIGHT-ROBUST</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>position BUY across all 7 weight sets</t>
+      <c r="C10" s="2" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>-34</v>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v>-25.3</v>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>HOLD under Set A''/Set A'/Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.9444</v>
+        <v>4.9446</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>4.56</v>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>16.4629</v>
+        <v>16.4636</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>18.9</v>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -1299,10 +1299,10 @@
         <v>16.59</v>
       </c>
       <c r="D9" t="n">
-        <v>14.41</v>
+        <v>13.87</v>
       </c>
       <c r="E9" t="n">
-        <v>-21.5</v>
+        <v>-24.4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>14.38</v>
+        <v>13.84</v>
       </c>
       <c r="H9" t="n">
-        <v>-21.7</v>
+        <v>-24.6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14.3</v>
+        <v>13.76</v>
       </c>
       <c r="K9" t="n">
-        <v>-22.1</v>
+        <v>-25</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13.58</v>
+        <v>13.04</v>
       </c>
       <c r="N9" t="n">
-        <v>-26</v>
+        <v>-28.9</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>13.82</v>
+        <v>13.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>-24.7</v>
+        <v>-27.6</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>13.25</v>
+        <v>12.71</v>
       </c>
       <c r="T9" t="n">
-        <v>-27.8</v>
+        <v>-30.7</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>13.52</v>
+        <v>12.98</v>
       </c>
       <c r="W9" t="n">
-        <v>-26.3</v>
+        <v>-29.2</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -799,10 +799,10 @@
         <v>30.5</v>
       </c>
       <c r="D4" t="n">
-        <v>27.79</v>
+        <v>28.29</v>
       </c>
       <c r="E4" t="n">
-        <v>-37.1</v>
+        <v>-36</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>27.57</v>
+        <v>28.09</v>
       </c>
       <c r="H4" t="n">
-        <v>-37.6</v>
+        <v>-36.4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>27.1</v>
+        <v>27.63</v>
       </c>
       <c r="K4" t="n">
-        <v>-38.7</v>
+        <v>-37.5</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>22.81</v>
+        <v>23.57</v>
       </c>
       <c r="N4" t="n">
-        <v>-48.4</v>
+        <v>-46.7</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>24.24</v>
+        <v>24.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>-45.2</v>
+        <v>-43.6</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>20.82</v>
+        <v>21.68</v>
       </c>
       <c r="T4" t="n">
-        <v>-52.9</v>
+        <v>-50.9</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>22.46</v>
+        <v>23.23</v>
       </c>
       <c r="W4" t="n">
-        <v>-49.2</v>
+        <v>-47.4</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>-54.7</v>
+        <v>-55.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H7" t="n">
-        <v>-54.9</v>
+        <v>-56</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="K7" t="n">
-        <v>-55.5</v>
+        <v>-56.6</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="N7" t="n">
-        <v>-61.7</v>
+        <v>-62.6</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>-59.7</v>
+        <v>-60.6</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="T7" t="n">
-        <v>-64.40000000000001</v>
+        <v>-65.2</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="W7" t="n">
-        <v>-62.1</v>
+        <v>-63</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -1499,43 +1499,43 @@
         <v>18.9</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>16.02</v>
+        <v>17.56</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-2.7</v>
+        <v>6.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>15.88</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
       <c r="M11" s="2" t="n">
-        <v>12.87</v>
+        <v>14.3</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-21.8</v>
+        <v>-13.1</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>13.76</v>
+        <v>15.22</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-16.4</v>
+        <v>-7.6</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="S11" s="2" t="n">
-        <v>11.62</v>
+        <v>12.98</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>-29.4</v>
+        <v>-21.2</v>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="V11" s="2" t="n">
-        <v>12.65</v>
+        <v>14.05</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>-23.2</v>
+        <v>-14.7</v>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A''/Set A'; TRIM/SHORT under Set A/Set B/Set C/Set D/Set E</t>
+          <t>BUY under Set A''/Set A'; HOLD under Set A; TRIM/SHORT under Set B/Set C/Set D/Set E</t>
         </is>
       </c>
     </row>

--- a/outputs/weight_robustness_diagnostic.xlsx
+++ b/outputs/weight_robustness_diagnostic.xlsx
@@ -1299,10 +1299,10 @@
         <v>16.59</v>
       </c>
       <c r="D9" t="n">
-        <v>13.87</v>
+        <v>13.63</v>
       </c>
       <c r="E9" t="n">
-        <v>-24.4</v>
+        <v>-25.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>13.84</v>
+        <v>13.6</v>
       </c>
       <c r="H9" t="n">
-        <v>-24.6</v>
+        <v>-25.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13.76</v>
+        <v>13.52</v>
       </c>
       <c r="K9" t="n">
-        <v>-25</v>
+        <v>-26.3</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1332,32 +1332,32 @@
         </is>
       </c>
       <c r="M9" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-30.2</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
         <v>13.04</v>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>13.28</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-27.6</v>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>12.71</v>
+        <v>12.47</v>
       </c>
       <c r="T9" t="n">
-        <v>-30.7</v>
+        <v>-32</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>12.98</v>
+        <v>12.75</v>
       </c>
       <c r="W9" t="n">
-        <v>-29.2</v>
+        <v>-30.5</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
